--- a/Übungen/Online_Shop.Projekt.xlsx
+++ b/Übungen/Online_Shop.Projekt.xlsx
@@ -5,14 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PSP" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="PSP_2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Netzplan" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Gantt" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Feiertage" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Gantt" sheetId="4" state="hidden" r:id="rId6"/>
+    <sheet name="Feiertage" sheetId="5" state="hidden" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="150">
   <si>
     <t xml:space="preserve">Beispiel: Funktionsorientierter Projektstrukturplan</t>
   </si>
@@ -322,6 +322,12 @@
   </si>
   <si>
     <t xml:space="preserve">Spätester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtpuffer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freier Puffer</t>
   </si>
   <si>
     <t xml:space="preserve">Ressourcen</t>
@@ -475,15 +481,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0.00\ %"/>
     <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="0\ %"/>
-    <numFmt numFmtId="169" formatCode="General"/>
-    <numFmt numFmtId="170" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="171" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
+    <numFmt numFmtId="169" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -593,7 +598,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor rgb="FFFF8080"/>
+        <bgColor rgb="FFFF8000"/>
       </patternFill>
     </fill>
     <fill>
@@ -675,7 +680,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="30">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -768,66 +773,198 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right style="hair"/>
-      <top style="hair"/>
-      <bottom style="hair"/>
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color rgb="FFFF8000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFFF8000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFFF8000"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFFF8000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF8000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="hair"/>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color rgb="FFFF8000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="medium"/>
-      <top style="medium"/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF8000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF8000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="hair"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF8000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF8000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="medium"/>
+      <right style="medium">
+        <color rgb="FFFF8000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right style="medium"/>
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF8000"/>
+      </right>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color rgb="FFFF8000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="hair"/>
-      <top style="medium"/>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF8000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="hair"/>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF8000"/>
+      </right>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color rgb="FFFF8000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF8000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFFF8000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair">
+        <color rgb="FFFF8000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFFF8000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFFF8000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -865,7 +1002,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="119">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1046,12 +1183,208 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="11" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="16" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="17" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="29" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="11" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="18" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="12" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1062,116 +1395,48 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="14" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="14" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="15" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="16" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="17" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1186,71 +1451,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="18" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="70" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1262,15 +1467,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1487,7 +1692,7 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FFCC0000"/>
@@ -1526,7 +1731,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFC000"/>
-      <rgbColor rgb="FFFFBF00"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF70AD47"/>
@@ -1554,9 +1759,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>102600</xdr:colOff>
+      <xdr:colOff>102240</xdr:colOff>
       <xdr:row>108</xdr:row>
-      <xdr:rowOff>146160</xdr:rowOff>
+      <xdr:rowOff>145800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1566,7 +1771,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7192440" y="17212320"/>
-          <a:ext cx="2242080" cy="421920"/>
+          <a:ext cx="2241720" cy="421560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1593,24 +1798,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="de-DE" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="de-DE" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
               <a:latin typeface="Cambria Math"/>
             </a:rPr>
-            <a:t>𝐷𝑎𝑢𝑒𝑟</a:t>
+            <a:t>𝐷𝑎𝑢𝑒𝑟=  (𝐴𝑢𝑓𝑤𝑎𝑛𝑑 (𝑃𝑇))/█((𝑃𝑒𝑟𝑠𝑜𝑛 ∗𝐾𝑎𝑝𝑎𝑧𝑖𝑡ä𝑡(%)))</a:t>
           </a:r>
-          <a:r>
-            <a:rPr b="0" lang="de-DE" sz="1100" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Cambria Math"/>
-            </a:rPr>
-            <a:t>=  (𝐴𝑢𝑓𝑤𝑎𝑛𝑑 (𝑃𝑇))/█((𝑃𝑒𝑟𝑠𝑜𝑛 ∗𝐾𝑎𝑝𝑎𝑧𝑖𝑡ä𝑡(%)))</a:t>
-          </a:r>
-          <a:endParaRPr b="0" lang="de-DE" sz="1100" spc="-1" strike="noStrike">
+          <a:endParaRPr b="0" lang="de-DE" sz="1100" strike="noStrike" u="none">
+            <a:effectLst/>
+            <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
@@ -1632,9 +1832,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>183960</xdr:colOff>
+      <xdr:colOff>183600</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>149760</xdr:rowOff>
+      <xdr:rowOff>149400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1644,7 +1844,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7922160" y="1632600"/>
-          <a:ext cx="110520" cy="161640"/>
+          <a:ext cx="110160" cy="161280"/>
         </a:xfrm>
         <a:prstGeom prst="diamond">
           <a:avLst/>
@@ -1676,9 +1876,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>183600</xdr:colOff>
+      <xdr:colOff>183240</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1080</xdr:rowOff>
+      <xdr:rowOff>720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1688,7 +1888,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12196440" y="2779560"/>
-          <a:ext cx="110520" cy="161640"/>
+          <a:ext cx="110160" cy="161280"/>
         </a:xfrm>
         <a:prstGeom prst="diamond">
           <a:avLst/>
@@ -1720,9 +1920,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
-      <xdr:colOff>183240</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>720</xdr:rowOff>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>162360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1732,7 +1932,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14207760" y="3264840"/>
-          <a:ext cx="110520" cy="161640"/>
+          <a:ext cx="110160" cy="161280"/>
         </a:xfrm>
         <a:prstGeom prst="diamond">
           <a:avLst/>
@@ -1936,7 +2136,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr defaultColWidth="13.00390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.00390625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.71"/>
   </cols>
@@ -2505,7 +2705,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M49"/>
-  <sheetFormatPr defaultColWidth="13.00390625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.00390625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.71"/>
   </cols>
@@ -3223,8 +3423,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BQ23"/>
-  <sheetFormatPr defaultColWidth="11.71484375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <dimension ref="A1:BQ24"/>
+  <sheetFormatPr defaultColWidth="11.71484375" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="16.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="11.57"/>
@@ -3238,1230 +3438,1252 @@
       <c r="A1" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="45" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="46" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="48" t="s">
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="49" t="n">
+      <c r="G2" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="50" t="n">
+      <c r="H2" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="49" t="n">
+      <c r="I2" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="52" t="n">
         <f aca="false">ROUND(G2/(H2*I2),0)</f>
         <v>2</v>
       </c>
-      <c r="L2" s="52" t="n">
+      <c r="L2" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="53"/>
-      <c r="N2" s="54" t="n">
+      <c r="M2" s="56"/>
+      <c r="N2" s="57" t="n">
         <f aca="false">L2+L4</f>
         <v>2</v>
       </c>
-      <c r="Q2" s="52" t="n">
+      <c r="Q2" s="55" t="n">
         <f aca="false">N2</f>
         <v>2</v>
       </c>
-      <c r="R2" s="53"/>
-      <c r="S2" s="54" t="n">
+      <c r="R2" s="56"/>
+      <c r="S2" s="57" t="n">
         <f aca="false">Q2+Q4</f>
         <v>3</v>
       </c>
-      <c r="V2" s="52" t="n">
+      <c r="V2" s="55" t="n">
         <f aca="false">S2</f>
         <v>3</v>
       </c>
-      <c r="W2" s="53"/>
-      <c r="X2" s="54" t="n">
+      <c r="W2" s="56"/>
+      <c r="X2" s="57" t="n">
         <f aca="false">V2+V4</f>
         <v>7</v>
       </c>
-      <c r="AF2" s="52" t="n">
+      <c r="AF2" s="55" t="n">
         <f aca="false">MAX(X2,AC8,X14)</f>
         <v>11</v>
       </c>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="54" t="n">
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="57" t="n">
         <f aca="false">AF2+AF4</f>
         <v>12</v>
       </c>
-      <c r="AK2" s="52" t="n">
+      <c r="AK2" s="55" t="n">
         <f aca="false">AH2</f>
         <v>12</v>
       </c>
-      <c r="AL2" s="53"/>
-      <c r="AM2" s="54" t="n">
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="57" t="n">
         <f aca="false">AK2+AK4</f>
         <v>13</v>
       </c>
-      <c r="AP2" s="52" t="n">
+      <c r="AP2" s="55" t="n">
         <f aca="false">AM2</f>
         <v>13</v>
       </c>
-      <c r="AQ2" s="53"/>
-      <c r="AR2" s="54" t="n">
+      <c r="AQ2" s="56"/>
+      <c r="AR2" s="57" t="n">
         <f aca="false">AP2+AP4</f>
         <v>14</v>
       </c>
-      <c r="AU2" s="52" t="n">
+      <c r="AU2" s="55" t="n">
         <f aca="false">AR2</f>
         <v>14</v>
       </c>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="54" t="n">
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="57" t="n">
         <f aca="false">AU2+AU4</f>
         <v>16</v>
       </c>
-      <c r="AZ2" s="52" t="n">
+      <c r="AZ2" s="55" t="n">
         <f aca="false">AW2</f>
         <v>16</v>
       </c>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="54" t="n">
+      <c r="BA2" s="56"/>
+      <c r="BB2" s="57" t="n">
         <f aca="false">AZ2+AZ4</f>
         <v>18</v>
       </c>
-      <c r="BE2" s="52" t="n">
+      <c r="BE2" s="55" t="n">
         <f aca="false">BB2</f>
         <v>18</v>
       </c>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="54" t="n">
+      <c r="BF2" s="56"/>
+      <c r="BG2" s="57" t="n">
         <f aca="false">BE2+BE4</f>
         <v>19</v>
       </c>
-      <c r="BJ2" s="52" t="n">
+      <c r="BJ2" s="55" t="n">
         <f aca="false">BG2</f>
         <v>19</v>
       </c>
-      <c r="BK2" s="53"/>
-      <c r="BL2" s="54" t="n">
+      <c r="BK2" s="56"/>
+      <c r="BL2" s="57" t="n">
         <f aca="false">BJ2+BJ4</f>
         <v>22</v>
       </c>
-      <c r="BO2" s="52" t="n">
+      <c r="BO2" s="55" t="n">
         <f aca="false">MAX(BL2,AC14)</f>
         <v>27</v>
       </c>
-      <c r="BP2" s="53"/>
-      <c r="BQ2" s="54" t="n">
+      <c r="BP2" s="56"/>
+      <c r="BQ2" s="57" t="n">
         <f aca="false">BO2+BO4</f>
         <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="55" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="57" t="n">
+      <c r="G3" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="56" t="n">
+      <c r="I3" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="61" t="n">
         <f aca="false">ROUND(G3/(H3*I3),0)</f>
         <v>1</v>
       </c>
-      <c r="L3" s="59" t="s">
+      <c r="L3" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="59"/>
-      <c r="N3" s="59"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="61"/>
-      <c r="Q3" s="59" t="s">
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="59" t="s">
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="59"/>
-      <c r="X3" s="59"/>
-      <c r="Y3" s="60"/>
-      <c r="Z3" s="62"/>
-      <c r="AA3" s="62"/>
-      <c r="AB3" s="62"/>
-      <c r="AC3" s="62"/>
-      <c r="AD3" s="62"/>
-      <c r="AE3" s="61"/>
-      <c r="AF3" s="59" t="s">
+      <c r="W3" s="64"/>
+      <c r="X3" s="64"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="67"/>
+      <c r="AA3" s="67"/>
+      <c r="AB3" s="67"/>
+      <c r="AC3" s="67"/>
+      <c r="AD3" s="67"/>
+      <c r="AE3" s="66"/>
+      <c r="AF3" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="60"/>
-      <c r="AJ3" s="61"/>
-      <c r="AK3" s="59" t="s">
+      <c r="AG3" s="64"/>
+      <c r="AH3" s="64"/>
+      <c r="AI3" s="65"/>
+      <c r="AJ3" s="66"/>
+      <c r="AK3" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59"/>
-      <c r="AN3" s="60"/>
-      <c r="AO3" s="61"/>
-      <c r="AP3" s="59" t="s">
+      <c r="AL3" s="64"/>
+      <c r="AM3" s="64"/>
+      <c r="AN3" s="65"/>
+      <c r="AO3" s="66"/>
+      <c r="AP3" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="60"/>
-      <c r="AT3" s="61"/>
-      <c r="AU3" s="59" t="s">
+      <c r="AQ3" s="64"/>
+      <c r="AR3" s="64"/>
+      <c r="AS3" s="65"/>
+      <c r="AT3" s="66"/>
+      <c r="AU3" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="59"/>
-      <c r="AX3" s="60"/>
-      <c r="AY3" s="61"/>
-      <c r="AZ3" s="59" t="s">
+      <c r="AV3" s="64"/>
+      <c r="AW3" s="64"/>
+      <c r="AX3" s="65"/>
+      <c r="AY3" s="66"/>
+      <c r="AZ3" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="60"/>
-      <c r="BD3" s="61"/>
-      <c r="BE3" s="59" t="s">
+      <c r="BA3" s="64"/>
+      <c r="BB3" s="64"/>
+      <c r="BC3" s="65"/>
+      <c r="BD3" s="66"/>
+      <c r="BE3" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="BF3" s="59"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="60"/>
-      <c r="BI3" s="61"/>
-      <c r="BJ3" s="59" t="s">
+      <c r="BF3" s="64"/>
+      <c r="BG3" s="64"/>
+      <c r="BH3" s="65"/>
+      <c r="BI3" s="66"/>
+      <c r="BJ3" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="BK3" s="59"/>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="60"/>
-      <c r="BN3" s="61"/>
-      <c r="BO3" s="59" t="s">
+      <c r="BK3" s="64"/>
+      <c r="BL3" s="64"/>
+      <c r="BM3" s="65"/>
+      <c r="BN3" s="66"/>
+      <c r="BO3" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="BP3" s="59"/>
-      <c r="BQ3" s="59"/>
+      <c r="BP3" s="64"/>
+      <c r="BQ3" s="64"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="55" t="s">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="56" t="n">
+      <c r="G4" s="61" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="H4" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="56" t="n">
+      <c r="I4" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="61" t="n">
         <f aca="false">ROUND(G4/(H4*I4),0)</f>
         <v>4</v>
       </c>
-      <c r="L4" s="63" t="n">
+      <c r="L4" s="68" t="n">
         <f aca="false">J2</f>
         <v>2</v>
       </c>
-      <c r="M4" s="64" t="n">
+      <c r="M4" s="69" t="n">
         <f aca="false">N5-N2</f>
         <v>0</v>
       </c>
-      <c r="N4" s="65" t="n">
+      <c r="N4" s="70" t="n">
         <f aca="false">MIN(Q2,Q14)-N2</f>
         <v>0</v>
       </c>
-      <c r="O4" s="66"/>
-      <c r="Q4" s="63" t="n">
+      <c r="O4" s="71"/>
+      <c r="Q4" s="68" t="n">
         <f aca="false">J3</f>
         <v>1</v>
       </c>
-      <c r="R4" s="64" t="n">
+      <c r="R4" s="69" t="n">
         <f aca="false">S5-S2</f>
         <v>5</v>
       </c>
-      <c r="S4" s="65" t="n">
+      <c r="S4" s="70" t="n">
         <f aca="false">MIN(V2,V8)-S2</f>
         <v>0</v>
       </c>
-      <c r="T4" s="66"/>
-      <c r="V4" s="63" t="n">
+      <c r="T4" s="71"/>
+      <c r="V4" s="68" t="n">
         <f aca="false">J4</f>
         <v>4</v>
       </c>
-      <c r="W4" s="64" t="n">
+      <c r="W4" s="69" t="n">
         <f aca="false">X5-X2</f>
         <v>9</v>
       </c>
-      <c r="X4" s="65" t="n">
+      <c r="X4" s="70" t="n">
         <f aca="false">AF2-X2</f>
         <v>4</v>
       </c>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="63" t="n">
+      <c r="AE4" s="72"/>
+      <c r="AF4" s="68" t="n">
         <f aca="false">J9</f>
         <v>1</v>
       </c>
-      <c r="AG4" s="64" t="n">
+      <c r="AG4" s="69" t="n">
         <f aca="false">AH5-AH2</f>
         <v>5</v>
       </c>
-      <c r="AH4" s="65" t="n">
+      <c r="AH4" s="70" t="n">
         <f aca="false">AK2-AH2</f>
         <v>0</v>
       </c>
-      <c r="AK4" s="63" t="n">
+      <c r="AK4" s="68" t="n">
         <f aca="false">J10</f>
         <v>1</v>
       </c>
-      <c r="AL4" s="64" t="n">
+      <c r="AL4" s="69" t="n">
         <f aca="false">AM5-AM2</f>
         <v>5</v>
       </c>
-      <c r="AM4" s="65" t="n">
+      <c r="AM4" s="70" t="n">
         <f aca="false">AP2-AM2</f>
         <v>0</v>
       </c>
-      <c r="AP4" s="63" t="n">
+      <c r="AP4" s="68" t="n">
         <f aca="false">J11</f>
         <v>1</v>
       </c>
-      <c r="AQ4" s="64" t="n">
+      <c r="AQ4" s="69" t="n">
         <f aca="false">AR5-AR2</f>
         <v>5</v>
       </c>
-      <c r="AR4" s="65" t="n">
+      <c r="AR4" s="70" t="n">
         <f aca="false">AU2-AR2</f>
         <v>0</v>
       </c>
-      <c r="AU4" s="63" t="n">
+      <c r="AU4" s="68" t="n">
         <f aca="false">J13</f>
         <v>2</v>
       </c>
-      <c r="AV4" s="64" t="n">
+      <c r="AV4" s="69" t="n">
         <f aca="false">AW5-AW2</f>
         <v>5</v>
       </c>
-      <c r="AW4" s="65" t="n">
+      <c r="AW4" s="70" t="n">
         <f aca="false">AZ2-AW2</f>
         <v>0</v>
       </c>
-      <c r="AZ4" s="63" t="n">
+      <c r="AZ4" s="68" t="n">
         <f aca="false">J14</f>
         <v>2</v>
       </c>
-      <c r="BA4" s="64" t="n">
+      <c r="BA4" s="69" t="n">
         <f aca="false">BB5-BB2</f>
         <v>5</v>
       </c>
-      <c r="BB4" s="65" t="n">
+      <c r="BB4" s="70" t="n">
         <f aca="false">BE2-BB2</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="63" t="n">
+      <c r="BE4" s="68" t="n">
         <f aca="false">J15</f>
         <v>1</v>
       </c>
-      <c r="BF4" s="64" t="n">
+      <c r="BF4" s="69" t="n">
         <f aca="false">BG5-BG2</f>
         <v>5</v>
       </c>
-      <c r="BG4" s="65" t="n">
+      <c r="BG4" s="70" t="n">
         <f aca="false">BJ2-BG2</f>
         <v>0</v>
       </c>
-      <c r="BJ4" s="63" t="n">
+      <c r="BJ4" s="68" t="n">
         <f aca="false">J16</f>
         <v>3</v>
       </c>
-      <c r="BK4" s="64" t="n">
+      <c r="BK4" s="69" t="n">
         <f aca="false">BL5-BL2</f>
         <v>5</v>
       </c>
-      <c r="BL4" s="65" t="n">
+      <c r="BL4" s="70" t="n">
         <f aca="false">BO2-BL2</f>
         <v>5</v>
       </c>
-      <c r="BN4" s="61"/>
-      <c r="BO4" s="63" t="n">
+      <c r="BN4" s="66"/>
+      <c r="BO4" s="68" t="n">
         <f aca="false">J17</f>
         <v>1</v>
       </c>
-      <c r="BP4" s="64" t="n">
+      <c r="BP4" s="69" t="n">
         <f aca="false">BQ5-BQ2</f>
         <v>0</v>
       </c>
-      <c r="BQ4" s="65"/>
+      <c r="BQ4" s="70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="55" t="s">
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="56" t="n">
+      <c r="G5" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="57" t="n">
+      <c r="H5" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="58" t="n">
+      <c r="I5" s="63" t="n">
         <f aca="false">120%/2</f>
         <v>0.6</v>
       </c>
-      <c r="J5" s="56" t="n">
+      <c r="J5" s="61" t="n">
         <f aca="false">ROUND(G5/(H5*I5),0)</f>
         <v>3</v>
       </c>
-      <c r="L5" s="68" t="n">
+      <c r="L5" s="73" t="n">
         <f aca="false">N5-L4</f>
         <v>0</v>
       </c>
-      <c r="M5" s="53"/>
-      <c r="N5" s="69" t="n">
+      <c r="M5" s="56"/>
+      <c r="N5" s="74" t="n">
         <f aca="false">MIN(Q5,Q17)</f>
         <v>2</v>
       </c>
-      <c r="O5" s="70"/>
-      <c r="Q5" s="68" t="n">
+      <c r="O5" s="75"/>
+      <c r="Q5" s="73" t="n">
         <f aca="false">S5-Q4</f>
         <v>7</v>
       </c>
-      <c r="R5" s="53"/>
-      <c r="S5" s="69" t="n">
+      <c r="R5" s="56"/>
+      <c r="S5" s="74" t="n">
         <f aca="false">MIN(V5,V11)</f>
         <v>8</v>
       </c>
-      <c r="T5" s="70"/>
-      <c r="V5" s="68" t="n">
+      <c r="T5" s="75"/>
+      <c r="V5" s="73" t="n">
         <f aca="false">X5-V4</f>
         <v>12</v>
       </c>
-      <c r="W5" s="53"/>
-      <c r="X5" s="69" t="n">
+      <c r="W5" s="56"/>
+      <c r="X5" s="74" t="n">
         <f aca="false">AF5</f>
         <v>16</v>
       </c>
-      <c r="AD5" s="70"/>
-      <c r="AF5" s="68" t="n">
+      <c r="AD5" s="75"/>
+      <c r="AF5" s="73" t="n">
         <f aca="false">AH5-AF4</f>
         <v>16</v>
       </c>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="69" t="n">
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="74" t="n">
         <f aca="false">AK5</f>
         <v>17</v>
       </c>
-      <c r="AK5" s="68" t="n">
+      <c r="AK5" s="73" t="n">
         <f aca="false">AM5-AK4</f>
         <v>17</v>
       </c>
-      <c r="AL5" s="53"/>
-      <c r="AM5" s="69" t="n">
+      <c r="AL5" s="56"/>
+      <c r="AM5" s="74" t="n">
         <f aca="false">AP5</f>
         <v>18</v>
       </c>
-      <c r="AP5" s="68" t="n">
+      <c r="AP5" s="73" t="n">
         <f aca="false">AR5-AP4</f>
         <v>18</v>
       </c>
-      <c r="AQ5" s="53"/>
-      <c r="AR5" s="69" t="n">
+      <c r="AQ5" s="56"/>
+      <c r="AR5" s="74" t="n">
         <f aca="false">AU5</f>
         <v>19</v>
       </c>
-      <c r="AU5" s="68" t="n">
+      <c r="AU5" s="73" t="n">
         <f aca="false">AW5-AU4</f>
         <v>19</v>
       </c>
-      <c r="AV5" s="53"/>
-      <c r="AW5" s="69" t="n">
+      <c r="AV5" s="56"/>
+      <c r="AW5" s="74" t="n">
         <f aca="false">AZ5</f>
         <v>21</v>
       </c>
-      <c r="AZ5" s="68" t="n">
+      <c r="AZ5" s="73" t="n">
         <f aca="false">BB5-AZ4</f>
         <v>21</v>
       </c>
-      <c r="BA5" s="53"/>
-      <c r="BB5" s="69" t="n">
+      <c r="BA5" s="56"/>
+      <c r="BB5" s="74" t="n">
         <f aca="false">BE5</f>
         <v>23</v>
       </c>
-      <c r="BE5" s="68" t="n">
+      <c r="BE5" s="73" t="n">
         <f aca="false">BG5-BE4</f>
         <v>23</v>
       </c>
-      <c r="BF5" s="53"/>
-      <c r="BG5" s="69" t="n">
+      <c r="BF5" s="56"/>
+      <c r="BG5" s="74" t="n">
         <f aca="false">BJ5</f>
         <v>24</v>
       </c>
-      <c r="BJ5" s="68" t="n">
+      <c r="BJ5" s="73" t="n">
         <f aca="false">BL5-BJ4</f>
         <v>24</v>
       </c>
-      <c r="BK5" s="53"/>
-      <c r="BL5" s="69" t="n">
+      <c r="BK5" s="56"/>
+      <c r="BL5" s="74" t="n">
         <f aca="false">BO5</f>
         <v>27</v>
       </c>
-      <c r="BM5" s="70"/>
-      <c r="BO5" s="68" t="n">
+      <c r="BM5" s="75"/>
+      <c r="BO5" s="73" t="n">
         <f aca="false">BQ5-BO4</f>
         <v>27</v>
       </c>
-      <c r="BP5" s="53"/>
-      <c r="BQ5" s="69" t="n">
+      <c r="BP5" s="56"/>
+      <c r="BQ5" s="74" t="n">
         <f aca="false">BQ2</f>
         <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="71" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="72" t="n">
+      <c r="G6" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="58" t="n">
+      <c r="H6" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J6" s="56" t="n">
+      <c r="J6" s="61" t="n">
         <f aca="false">ROUND(G6/(H6*I6),0)</f>
         <v>5</v>
       </c>
-      <c r="O6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="70"/>
-      <c r="BM6" s="70"/>
+      <c r="O6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="75"/>
+      <c r="BM6" s="75"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="55" t="s">
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="57" t="s">
+      <c r="G7" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I7" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="56" t="n">
+      <c r="I7" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="61" t="n">
         <f aca="false">ROUND(G7/(H7*I7),0)</f>
         <v>1</v>
       </c>
-      <c r="O7" s="70"/>
-      <c r="T7" s="70"/>
-      <c r="AD7" s="70"/>
-      <c r="AE7" s="70"/>
-      <c r="BM7" s="70"/>
+      <c r="O7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75"/>
+      <c r="BM7" s="75"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="71" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="72" t="n">
+      <c r="G8" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="57" t="s">
+      <c r="H8" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="58" t="n">
+      <c r="I8" s="63" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="56" t="n">
+      <c r="J8" s="61" t="n">
         <f aca="false">ROUND(G8/(H8*I8),0)</f>
         <v>4</v>
       </c>
-      <c r="O8" s="70"/>
-      <c r="T8" s="70"/>
-      <c r="V8" s="52" t="n">
+      <c r="O8" s="75"/>
+      <c r="T8" s="75"/>
+      <c r="V8" s="55" t="n">
         <f aca="false">S2</f>
         <v>3</v>
       </c>
-      <c r="W8" s="53"/>
-      <c r="X8" s="54" t="n">
+      <c r="W8" s="56"/>
+      <c r="X8" s="57" t="n">
         <f aca="false">V8+V10</f>
         <v>6</v>
       </c>
-      <c r="AA8" s="52" t="n">
+      <c r="AA8" s="55" t="n">
         <f aca="false">X8</f>
         <v>6</v>
       </c>
-      <c r="AB8" s="53"/>
-      <c r="AC8" s="54" t="n">
+      <c r="AB8" s="56"/>
+      <c r="AC8" s="57" t="n">
         <f aca="false">AA8+AA10</f>
         <v>11</v>
       </c>
-      <c r="AD8" s="70"/>
-      <c r="AE8" s="70"/>
-      <c r="BM8" s="70"/>
+      <c r="AD8" s="75"/>
+      <c r="AE8" s="75"/>
+      <c r="BM8" s="75"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="71" t="s">
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="72" t="n">
+      <c r="G9" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I9" s="58" t="n">
+      <c r="I9" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J9" s="56" t="n">
+      <c r="J9" s="61" t="n">
         <f aca="false">ROUND(G9/(H9*I9),0)</f>
         <v>1</v>
       </c>
-      <c r="O9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="V9" s="59" t="s">
+      <c r="O9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="V9" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="W9" s="59"/>
-      <c r="X9" s="59"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="61"/>
-      <c r="AA9" s="59" t="s">
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="65"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="AB9" s="59"/>
-      <c r="AC9" s="59"/>
-      <c r="AD9" s="73"/>
-      <c r="AE9" s="70"/>
-      <c r="BM9" s="70"/>
+      <c r="AB9" s="64"/>
+      <c r="AC9" s="64"/>
+      <c r="AD9" s="78"/>
+      <c r="AE9" s="75"/>
+      <c r="BM9" s="75"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="71" t="s">
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="72" t="n">
+      <c r="G10" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="57" t="s">
+      <c r="H10" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I10" s="58" t="n">
+      <c r="I10" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J10" s="56" t="n">
+      <c r="J10" s="61" t="n">
         <f aca="false">ROUND(G10/(H10*I10),0)</f>
         <v>1</v>
       </c>
-      <c r="O10" s="70"/>
-      <c r="U10" s="74"/>
-      <c r="V10" s="63" t="n">
+      <c r="O10" s="75"/>
+      <c r="U10" s="79"/>
+      <c r="V10" s="68" t="n">
         <f aca="false">J5</f>
         <v>3</v>
       </c>
-      <c r="W10" s="64" t="n">
+      <c r="W10" s="69" t="n">
         <f aca="false">X11-X8</f>
         <v>5</v>
       </c>
-      <c r="X10" s="65" t="n">
+      <c r="X10" s="70" t="n">
         <f aca="false">AA8-X8</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="63" t="n">
+      <c r="AA10" s="68" t="n">
         <f aca="false">J6</f>
         <v>5</v>
       </c>
-      <c r="AB10" s="64" t="n">
+      <c r="AB10" s="69" t="n">
         <f aca="false">AC11-AC8</f>
         <v>5</v>
       </c>
-      <c r="AC10" s="65" t="n">
+      <c r="AC10" s="70" t="n">
         <f aca="false">AF2-AC8</f>
         <v>0</v>
       </c>
-      <c r="AE10" s="70"/>
-      <c r="BM10" s="70"/>
+      <c r="AE10" s="75"/>
+      <c r="BM10" s="75"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="71" t="s">
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="72" t="n">
+      <c r="G11" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="57" t="s">
+      <c r="H11" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I11" s="58" t="n">
+      <c r="I11" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J11" s="56" t="n">
+      <c r="J11" s="61" t="n">
         <f aca="false">ROUND(G11/(H11*I11),0)</f>
         <v>1</v>
       </c>
-      <c r="O11" s="70"/>
-      <c r="V11" s="68" t="n">
+      <c r="O11" s="75"/>
+      <c r="V11" s="73" t="n">
         <f aca="false">X11-V10</f>
         <v>8</v>
       </c>
-      <c r="W11" s="53"/>
-      <c r="X11" s="69" t="n">
+      <c r="W11" s="56"/>
+      <c r="X11" s="74" t="n">
         <f aca="false">AA11</f>
         <v>11</v>
       </c>
-      <c r="AA11" s="68" t="n">
+      <c r="AA11" s="73" t="n">
         <f aca="false">AC11-AA10</f>
         <v>11</v>
       </c>
-      <c r="AB11" s="53"/>
-      <c r="AC11" s="69" t="n">
+      <c r="AB11" s="56"/>
+      <c r="AC11" s="74" t="n">
         <f aca="false">AF5</f>
         <v>16</v>
       </c>
-      <c r="AE11" s="70"/>
-      <c r="BM11" s="70"/>
+      <c r="AE11" s="75"/>
+      <c r="BM11" s="75"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="71" t="s">
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="72" t="n">
+      <c r="G12" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="58" t="n">
+      <c r="H12" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="63" t="n">
         <v>0.5</v>
       </c>
-      <c r="J12" s="56" t="n">
+      <c r="J12" s="61" t="n">
         <f aca="false">ROUND(G12/(H12*I12),0)</f>
         <v>20</v>
       </c>
-      <c r="O12" s="70"/>
-      <c r="Z12" s="62"/>
-      <c r="AA12" s="62"/>
-      <c r="AB12" s="62"/>
-      <c r="AC12" s="62"/>
-      <c r="AD12" s="62"/>
-      <c r="AE12" s="75"/>
-      <c r="BM12" s="70"/>
+      <c r="O12" s="75"/>
+      <c r="Z12" s="67"/>
+      <c r="AA12" s="67"/>
+      <c r="AB12" s="67"/>
+      <c r="AC12" s="67"/>
+      <c r="AD12" s="67"/>
+      <c r="AE12" s="80"/>
+      <c r="BM12" s="75"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="71" t="s">
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="71" t="s">
+      <c r="F13" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="72" t="n">
+      <c r="G13" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="58" t="n">
+      <c r="I13" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J13" s="56" t="n">
+      <c r="J13" s="61" t="n">
         <f aca="false">ROUND(G13/(H13*I13),0)</f>
         <v>2</v>
       </c>
-      <c r="O13" s="70"/>
-      <c r="Y13" s="70"/>
-      <c r="BM13" s="70"/>
+      <c r="O13" s="75"/>
+      <c r="Y13" s="75"/>
+      <c r="BM13" s="75"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="71" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="71" t="s">
+      <c r="F14" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="72" t="n">
+      <c r="G14" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="57" t="s">
+      <c r="H14" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I14" s="58" t="n">
+      <c r="I14" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J14" s="56" t="n">
+      <c r="J14" s="61" t="n">
         <f aca="false">ROUND(G14/(H14*I14),0)</f>
         <v>2</v>
       </c>
-      <c r="O14" s="70"/>
-      <c r="Q14" s="52" t="n">
+      <c r="O14" s="75"/>
+      <c r="Q14" s="55" t="n">
         <f aca="false">N2</f>
         <v>2</v>
       </c>
-      <c r="R14" s="53"/>
-      <c r="S14" s="54" t="n">
+      <c r="R14" s="56"/>
+      <c r="S14" s="57" t="n">
         <f aca="false">Q14+Q16</f>
         <v>3</v>
       </c>
-      <c r="V14" s="52" t="n">
+      <c r="V14" s="55" t="n">
         <f aca="false">S14</f>
         <v>3</v>
       </c>
-      <c r="W14" s="53"/>
-      <c r="X14" s="54" t="n">
+      <c r="W14" s="56"/>
+      <c r="X14" s="57" t="n">
         <f aca="false">V14+V16</f>
         <v>7</v>
       </c>
-      <c r="Y14" s="73"/>
-      <c r="AA14" s="52" t="n">
+      <c r="Y14" s="78"/>
+      <c r="AA14" s="55" t="n">
         <f aca="false">X14</f>
         <v>7</v>
       </c>
-      <c r="AB14" s="53"/>
-      <c r="AC14" s="54" t="n">
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="57" t="n">
         <f aca="false">AA14+AA16</f>
         <v>27</v>
       </c>
-      <c r="BM14" s="70"/>
+      <c r="BM14" s="75"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="71" t="s">
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="57" t="s">
+      <c r="G15" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I15" s="58" t="n">
+      <c r="I15" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J15" s="56" t="n">
+      <c r="J15" s="61" t="n">
         <f aca="false">ROUND(G15/(H15*I15),0)</f>
         <v>1</v>
       </c>
-      <c r="O15" s="70"/>
-      <c r="P15" s="76"/>
-      <c r="Q15" s="59" t="s">
+      <c r="O15" s="75"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="R15" s="59"/>
-      <c r="S15" s="59"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="61"/>
-      <c r="V15" s="59" t="s">
+      <c r="R15" s="64"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="W15" s="59"/>
-      <c r="X15" s="59"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="61"/>
-      <c r="AA15" s="59" t="s">
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="65"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="AB15" s="59"/>
-      <c r="AC15" s="59"/>
-      <c r="AD15" s="60"/>
-      <c r="AE15" s="62"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="62"/>
-      <c r="AM15" s="62"/>
-      <c r="AN15" s="62"/>
-      <c r="AO15" s="62"/>
-      <c r="AP15" s="62"/>
-      <c r="AQ15" s="62"/>
-      <c r="AR15" s="62"/>
-      <c r="AS15" s="62"/>
-      <c r="AT15" s="62"/>
-      <c r="AU15" s="62"/>
-      <c r="AV15" s="62"/>
-      <c r="AW15" s="62"/>
-      <c r="AX15" s="62"/>
-      <c r="AY15" s="62"/>
-      <c r="AZ15" s="62"/>
-      <c r="BA15" s="62"/>
-      <c r="BB15" s="62"/>
-      <c r="BC15" s="62"/>
-      <c r="BD15" s="62"/>
-      <c r="BE15" s="62"/>
-      <c r="BF15" s="62"/>
-      <c r="BG15" s="62"/>
-      <c r="BH15" s="62"/>
-      <c r="BI15" s="62"/>
-      <c r="BJ15" s="62"/>
-      <c r="BK15" s="62"/>
-      <c r="BL15" s="62"/>
-      <c r="BM15" s="75"/>
+      <c r="AB15" s="64"/>
+      <c r="AC15" s="64"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="67"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="67"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="67"/>
+      <c r="AL15" s="67"/>
+      <c r="AM15" s="67"/>
+      <c r="AN15" s="67"/>
+      <c r="AO15" s="67"/>
+      <c r="AP15" s="67"/>
+      <c r="AQ15" s="67"/>
+      <c r="AR15" s="67"/>
+      <c r="AS15" s="67"/>
+      <c r="AT15" s="67"/>
+      <c r="AU15" s="67"/>
+      <c r="AV15" s="67"/>
+      <c r="AW15" s="67"/>
+      <c r="AX15" s="67"/>
+      <c r="AY15" s="67"/>
+      <c r="AZ15" s="67"/>
+      <c r="BA15" s="67"/>
+      <c r="BB15" s="67"/>
+      <c r="BC15" s="67"/>
+      <c r="BD15" s="67"/>
+      <c r="BE15" s="67"/>
+      <c r="BF15" s="67"/>
+      <c r="BG15" s="67"/>
+      <c r="BH15" s="67"/>
+      <c r="BI15" s="67"/>
+      <c r="BJ15" s="67"/>
+      <c r="BK15" s="67"/>
+      <c r="BL15" s="67"/>
+      <c r="BM15" s="80"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="71" t="s">
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="72" t="n">
+      <c r="G16" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="57" t="s">
+      <c r="H16" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I16" s="58" t="n">
+      <c r="I16" s="63" t="n">
         <f aca="false">100%+(100%-$I$12)</f>
         <v>1.5</v>
       </c>
-      <c r="J16" s="56" t="n">
+      <c r="J16" s="61" t="n">
         <f aca="false">ROUND(G16/(H16*I16),0)</f>
         <v>3</v>
       </c>
-      <c r="Q16" s="63" t="n">
+      <c r="Q16" s="68" t="n">
         <f aca="false">J7</f>
         <v>1</v>
       </c>
-      <c r="R16" s="64" t="n">
+      <c r="R16" s="69" t="n">
         <f aca="false">S17-S14</f>
         <v>0</v>
       </c>
-      <c r="S16" s="65" t="n">
+      <c r="S16" s="70" t="n">
         <f aca="false">V14-S14</f>
         <v>0</v>
       </c>
-      <c r="V16" s="63" t="n">
+      <c r="V16" s="68" t="n">
         <f aca="false">J8</f>
         <v>4</v>
       </c>
-      <c r="W16" s="64" t="n">
+      <c r="W16" s="69" t="n">
         <f aca="false">X17-X14</f>
         <v>0</v>
       </c>
-      <c r="X16" s="65" t="n">
+      <c r="X16" s="70" t="n">
         <f aca="false">MIN(AA14,AF2)-X14</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="63" t="n">
+      <c r="AA16" s="68" t="n">
         <f aca="false">J12</f>
         <v>20</v>
       </c>
-      <c r="AB16" s="64" t="n">
+      <c r="AB16" s="69" t="n">
         <f aca="false">AC17-AC14</f>
         <v>0</v>
       </c>
-      <c r="AC16" s="65" t="n">
+      <c r="AC16" s="70" t="n">
         <f aca="false">BO2-AC14</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="77" t="s">
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="78"/>
-      <c r="G17" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="80" t="s">
+      <c r="F17" s="85"/>
+      <c r="G17" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="79" t="n">
+      <c r="I17" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="86" t="n">
         <f aca="false">ROUND(G17/(H17*I17),0)</f>
         <v>1</v>
       </c>
-      <c r="Q17" s="68" t="n">
+      <c r="Q17" s="73" t="n">
         <f aca="false">S17-Q16</f>
         <v>2</v>
       </c>
-      <c r="R17" s="53"/>
-      <c r="S17" s="69" t="n">
+      <c r="R17" s="56"/>
+      <c r="S17" s="74" t="n">
         <f aca="false">V17</f>
         <v>3</v>
       </c>
-      <c r="V17" s="68" t="n">
+      <c r="V17" s="73" t="n">
         <f aca="false">X17-V16</f>
         <v>3</v>
       </c>
-      <c r="W17" s="53"/>
-      <c r="X17" s="69" t="n">
+      <c r="W17" s="56"/>
+      <c r="X17" s="74" t="n">
         <f aca="false">MIN(AA17,AF5)</f>
         <v>7</v>
       </c>
-      <c r="AA17" s="68" t="n">
+      <c r="AA17" s="73" t="n">
         <f aca="false">AC17-AA16</f>
         <v>7</v>
       </c>
-      <c r="AB17" s="53"/>
-      <c r="AC17" s="69" t="n">
+      <c r="AB17" s="56"/>
+      <c r="AC17" s="74" t="n">
         <f aca="false">BO5</f>
         <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="88"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="82" t="s">
+      <c r="A19" s="89" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="90" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="54" t="s">
+      <c r="B20" s="56"/>
+      <c r="C20" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="83" t="s">
+      <c r="D20" s="90" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="N21" s="0"/>
+      <c r="O21" s="0"/>
+      <c r="P21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="83" t="s">
+      <c r="D22" s="90" t="s">
         <v>95</v>
       </c>
+      <c r="N22" s="0"/>
+      <c r="O22" s="0"/>
+      <c r="P22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="69" t="s">
+      <c r="B23" s="56"/>
+      <c r="C23" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="83" t="s">
+      <c r="D23" s="90" t="s">
         <v>98</v>
       </c>
+      <c r="N23" s="0"/>
+      <c r="O23" s="0"/>
+      <c r="P23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="N24" s="0"/>
+      <c r="O24" s="0"/>
+      <c r="P24" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -4603,7 +4825,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BN20"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="2"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="5" min="5" style="44" width="16.14"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="1" max="6" min="6" style="44" width="11.57"/>
@@ -4623,189 +4845,189 @@
       </c>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="85" t="s">
+      <c r="G1" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="85" t="s">
+      <c r="H1" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="86" t="s">
+      <c r="I1" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="J1" s="85" t="s">
+      <c r="J1" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="85"/>
-      <c r="L1" s="87" t="n">
+      <c r="K1" s="92"/>
+      <c r="L1" s="94" t="n">
         <v>45397</v>
       </c>
-      <c r="M1" s="87" t="n">
+      <c r="M1" s="94" t="n">
         <v>45398</v>
       </c>
-      <c r="N1" s="87" t="n">
+      <c r="N1" s="94" t="n">
         <v>45399</v>
       </c>
-      <c r="O1" s="87" t="n">
+      <c r="O1" s="94" t="n">
         <v>45400</v>
       </c>
-      <c r="P1" s="87" t="n">
+      <c r="P1" s="94" t="n">
         <v>45401</v>
       </c>
-      <c r="Q1" s="87" t="n">
+      <c r="Q1" s="94" t="n">
         <v>45402</v>
       </c>
-      <c r="R1" s="87" t="n">
+      <c r="R1" s="94" t="n">
         <v>45403</v>
       </c>
-      <c r="S1" s="87" t="n">
+      <c r="S1" s="94" t="n">
         <v>45404</v>
       </c>
-      <c r="T1" s="87" t="n">
+      <c r="T1" s="94" t="n">
         <v>45405</v>
       </c>
-      <c r="U1" s="87" t="n">
+      <c r="U1" s="94" t="n">
         <v>45406</v>
       </c>
-      <c r="V1" s="87" t="n">
+      <c r="V1" s="94" t="n">
         <v>45407</v>
       </c>
-      <c r="W1" s="87" t="n">
+      <c r="W1" s="94" t="n">
         <v>45408</v>
       </c>
-      <c r="X1" s="87" t="n">
+      <c r="X1" s="94" t="n">
         <v>45409</v>
       </c>
-      <c r="Y1" s="87" t="n">
+      <c r="Y1" s="94" t="n">
         <v>45410</v>
       </c>
-      <c r="Z1" s="87" t="n">
+      <c r="Z1" s="94" t="n">
         <v>45411</v>
       </c>
-      <c r="AA1" s="87" t="n">
+      <c r="AA1" s="94" t="n">
         <v>45412</v>
       </c>
-      <c r="AB1" s="88" t="n">
+      <c r="AB1" s="95" t="n">
         <v>45413</v>
       </c>
-      <c r="AC1" s="87" t="n">
+      <c r="AC1" s="94" t="n">
         <v>45414</v>
       </c>
-      <c r="AD1" s="87" t="n">
+      <c r="AD1" s="94" t="n">
         <v>45415</v>
       </c>
-      <c r="AE1" s="87" t="n">
+      <c r="AE1" s="94" t="n">
         <v>45416</v>
       </c>
-      <c r="AF1" s="87" t="n">
+      <c r="AF1" s="94" t="n">
         <v>45417</v>
       </c>
-      <c r="AG1" s="87" t="n">
+      <c r="AG1" s="94" t="n">
         <v>45418</v>
       </c>
-      <c r="AH1" s="87" t="n">
+      <c r="AH1" s="94" t="n">
         <v>45419</v>
       </c>
-      <c r="AI1" s="87" t="n">
+      <c r="AI1" s="94" t="n">
         <v>45420</v>
       </c>
-      <c r="AJ1" s="88" t="n">
+      <c r="AJ1" s="95" t="n">
         <v>45421</v>
       </c>
-      <c r="AK1" s="87" t="n">
+      <c r="AK1" s="94" t="n">
         <v>45422</v>
       </c>
-      <c r="AL1" s="87" t="n">
+      <c r="AL1" s="94" t="n">
         <v>45423</v>
       </c>
-      <c r="AM1" s="87" t="n">
+      <c r="AM1" s="94" t="n">
         <v>45424</v>
       </c>
-      <c r="AN1" s="87" t="n">
+      <c r="AN1" s="94" t="n">
         <v>45425</v>
       </c>
-      <c r="AO1" s="87" t="n">
+      <c r="AO1" s="94" t="n">
         <v>45426</v>
       </c>
-      <c r="AP1" s="87" t="n">
+      <c r="AP1" s="94" t="n">
         <v>45427</v>
       </c>
-      <c r="AQ1" s="87" t="n">
+      <c r="AQ1" s="94" t="n">
         <v>45428</v>
       </c>
-      <c r="AR1" s="87" t="n">
+      <c r="AR1" s="94" t="n">
         <v>45429</v>
       </c>
-      <c r="AS1" s="87" t="n">
+      <c r="AS1" s="94" t="n">
         <v>45430</v>
       </c>
-      <c r="AT1" s="87" t="n">
+      <c r="AT1" s="94" t="n">
         <v>45431</v>
       </c>
-      <c r="AU1" s="87" t="n">
+      <c r="AU1" s="94" t="n">
         <v>45432</v>
       </c>
-      <c r="AV1" s="87" t="n">
+      <c r="AV1" s="94" t="n">
         <v>45433</v>
       </c>
-      <c r="AW1" s="87" t="n">
+      <c r="AW1" s="94" t="n">
         <v>45434</v>
       </c>
-      <c r="AX1" s="87" t="n">
+      <c r="AX1" s="94" t="n">
         <v>45435</v>
       </c>
-      <c r="AY1" s="87" t="n">
+      <c r="AY1" s="94" t="n">
         <v>45436</v>
       </c>
-      <c r="AZ1" s="87" t="n">
+      <c r="AZ1" s="94" t="n">
         <v>45437</v>
       </c>
-      <c r="BA1" s="87" t="n">
+      <c r="BA1" s="94" t="n">
         <v>45438</v>
       </c>
-      <c r="BB1" s="87" t="n">
+      <c r="BB1" s="94" t="n">
         <v>45439</v>
       </c>
-      <c r="BC1" s="87" t="n">
+      <c r="BC1" s="94" t="n">
         <v>45440</v>
       </c>
-      <c r="BD1" s="87" t="n">
+      <c r="BD1" s="94" t="n">
         <v>45441</v>
       </c>
-      <c r="BE1" s="88" t="n">
+      <c r="BE1" s="95" t="n">
         <v>45442</v>
       </c>
-      <c r="BF1" s="87" t="n">
+      <c r="BF1" s="94" t="n">
         <v>45443</v>
       </c>
-      <c r="BG1" s="87" t="n">
+      <c r="BG1" s="94" t="n">
         <v>45444</v>
       </c>
-      <c r="BH1" s="87" t="n">
+      <c r="BH1" s="94" t="n">
         <v>45445</v>
       </c>
-      <c r="BI1" s="87" t="n">
+      <c r="BI1" s="94" t="n">
         <v>45446</v>
       </c>
-      <c r="BJ1" s="87" t="n">
+      <c r="BJ1" s="94" t="n">
         <v>45447</v>
       </c>
-      <c r="BK1" s="87" t="n">
+      <c r="BK1" s="94" t="n">
         <v>45448</v>
       </c>
-      <c r="BL1" s="87" t="n">
+      <c r="BL1" s="94" t="n">
         <v>45449</v>
       </c>
-      <c r="BM1" s="87" t="n">
+      <c r="BM1" s="94" t="n">
         <v>45450</v>
       </c>
-      <c r="BN1" s="83" t="s">
-        <v>99</v>
+      <c r="BN1" s="90" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4817,39 +5039,39 @@
       </c>
       <c r="C2" s="34"/>
       <c r="D2" s="34"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="56" t="n">
+      <c r="G2" s="98" t="n">
         <f aca="false">Netzplan!G2</f>
         <v>5</v>
       </c>
-      <c r="H2" s="57" t="n">
+      <c r="H2" s="99" t="n">
         <f aca="false">Netzplan!H2</f>
         <v>3</v>
       </c>
-      <c r="I2" s="58" t="n">
+      <c r="I2" s="100" t="n">
         <f aca="false">Netzplan!I2</f>
         <v>1</v>
       </c>
-      <c r="J2" s="89" t="n">
+      <c r="J2" s="101" t="n">
         <f aca="false">Netzplan!J2</f>
         <v>2</v>
       </c>
-      <c r="K2" s="90" t="n">
+      <c r="K2" s="102" t="n">
         <f aca="false">SUM(L2:BM2)</f>
         <v>2</v>
       </c>
-      <c r="L2" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
+      <c r="L2" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="98"/>
       <c r="Q2" s="38"/>
       <c r="R2" s="38"/>
       <c r="S2" s="38"/>
@@ -4861,7 +5083,7 @@
       <c r="Y2" s="38"/>
       <c r="Z2" s="38"/>
       <c r="AA2" s="38"/>
-      <c r="AB2" s="91"/>
+      <c r="AB2" s="103"/>
       <c r="AC2" s="38"/>
       <c r="AD2" s="38"/>
       <c r="AE2" s="38"/>
@@ -4869,7 +5091,7 @@
       <c r="AG2" s="38"/>
       <c r="AH2" s="38"/>
       <c r="AI2" s="38"/>
-      <c r="AJ2" s="91"/>
+      <c r="AJ2" s="103"/>
       <c r="AK2" s="38"/>
       <c r="AL2" s="38"/>
       <c r="AM2" s="38"/>
@@ -4884,23 +5106,23 @@
       <c r="AV2" s="38"/>
       <c r="AW2" s="38"/>
       <c r="AX2" s="38"/>
-      <c r="AY2" s="92"/>
+      <c r="AY2" s="104"/>
       <c r="AZ2" s="38"/>
       <c r="BA2" s="38"/>
       <c r="BB2" s="38"/>
       <c r="BC2" s="38"/>
       <c r="BD2" s="38"/>
-      <c r="BE2" s="91"/>
-      <c r="BF2" s="92"/>
+      <c r="BE2" s="103"/>
+      <c r="BF2" s="104"/>
       <c r="BG2" s="38"/>
       <c r="BH2" s="38"/>
       <c r="BI2" s="38"/>
       <c r="BJ2" s="38"/>
       <c r="BK2" s="38"/>
-      <c r="BL2" s="92"/>
+      <c r="BL2" s="104"/>
       <c r="BM2" s="38"/>
       <c r="BN2" s="44" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4912,29 +5134,29 @@
       </c>
       <c r="C3" s="37"/>
       <c r="D3" s="37"/>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="105" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="56" t="n">
+      <c r="G3" s="98" t="n">
         <f aca="false">Netzplan!G3</f>
         <v>1</v>
       </c>
-      <c r="H3" s="57" t="n">
+      <c r="H3" s="99" t="n">
         <f aca="false">Netzplan!H3</f>
         <v>2</v>
       </c>
-      <c r="I3" s="58" t="n">
+      <c r="I3" s="100" t="n">
         <f aca="false">Netzplan!I3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="89" t="n">
+      <c r="J3" s="101" t="n">
         <f aca="false">Netzplan!J3</f>
         <v>1</v>
       </c>
-      <c r="K3" s="90" t="n">
+      <c r="K3" s="102" t="n">
         <f aca="false">SUM(L3:BM3)</f>
         <v>1</v>
       </c>
@@ -4947,7 +5169,7 @@
       <c r="P3" s="38"/>
       <c r="Q3" s="38"/>
       <c r="R3" s="38"/>
-      <c r="S3" s="56"/>
+      <c r="S3" s="98"/>
       <c r="T3" s="38"/>
       <c r="U3" s="38"/>
       <c r="V3" s="38"/>
@@ -4956,7 +5178,7 @@
       <c r="Y3" s="38"/>
       <c r="Z3" s="38"/>
       <c r="AA3" s="38"/>
-      <c r="AB3" s="91"/>
+      <c r="AB3" s="103"/>
       <c r="AC3" s="38"/>
       <c r="AD3" s="38"/>
       <c r="AE3" s="38"/>
@@ -4964,7 +5186,7 @@
       <c r="AG3" s="38"/>
       <c r="AH3" s="38"/>
       <c r="AI3" s="38"/>
-      <c r="AJ3" s="91"/>
+      <c r="AJ3" s="103"/>
       <c r="AK3" s="38"/>
       <c r="AL3" s="38"/>
       <c r="AM3" s="38"/>
@@ -4979,20 +5201,20 @@
       <c r="AV3" s="38"/>
       <c r="AW3" s="38"/>
       <c r="AX3" s="38"/>
-      <c r="AY3" s="92"/>
+      <c r="AY3" s="104"/>
       <c r="AZ3" s="38"/>
       <c r="BA3" s="38"/>
       <c r="BB3" s="38"/>
       <c r="BC3" s="38"/>
       <c r="BD3" s="38"/>
-      <c r="BE3" s="91"/>
-      <c r="BF3" s="92"/>
+      <c r="BE3" s="103"/>
+      <c r="BF3" s="104"/>
       <c r="BG3" s="38"/>
       <c r="BH3" s="38"/>
       <c r="BI3" s="38"/>
       <c r="BJ3" s="38"/>
       <c r="BK3" s="38"/>
-      <c r="BL3" s="92"/>
+      <c r="BL3" s="104"/>
       <c r="BM3" s="38"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5004,29 +5226,29 @@
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="37"/>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="56" t="n">
+      <c r="G4" s="98" t="n">
         <f aca="false">Netzplan!G4</f>
         <v>4</v>
       </c>
-      <c r="H4" s="56" t="str">
+      <c r="H4" s="98" t="str">
         <f aca="false">Netzplan!H4</f>
         <v>1</v>
       </c>
-      <c r="I4" s="58" t="n">
+      <c r="I4" s="100" t="n">
         <f aca="false">Netzplan!I4</f>
         <v>1</v>
       </c>
-      <c r="J4" s="89" t="n">
+      <c r="J4" s="101" t="n">
         <f aca="false">Netzplan!J4</f>
         <v>4</v>
       </c>
-      <c r="K4" s="90" t="n">
+      <c r="K4" s="102" t="n">
         <f aca="false">SUM(L4:BM4)</f>
         <v>4</v>
       </c>
@@ -5044,17 +5266,17 @@
       <c r="S4" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="T4" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
+      <c r="T4" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="98"/>
+      <c r="V4" s="98"/>
+      <c r="W4" s="98"/>
       <c r="X4" s="38"/>
       <c r="Y4" s="38"/>
       <c r="Z4" s="38"/>
       <c r="AA4" s="38"/>
-      <c r="AB4" s="91"/>
+      <c r="AB4" s="103"/>
       <c r="AC4" s="38"/>
       <c r="AD4" s="38"/>
       <c r="AE4" s="38"/>
@@ -5062,7 +5284,7 @@
       <c r="AG4" s="38"/>
       <c r="AH4" s="38"/>
       <c r="AI4" s="38"/>
-      <c r="AJ4" s="91"/>
+      <c r="AJ4" s="103"/>
       <c r="AK4" s="38"/>
       <c r="AL4" s="38"/>
       <c r="AM4" s="38"/>
@@ -5077,20 +5299,20 @@
       <c r="AV4" s="38"/>
       <c r="AW4" s="38"/>
       <c r="AX4" s="38"/>
-      <c r="AY4" s="92"/>
+      <c r="AY4" s="104"/>
       <c r="AZ4" s="38"/>
       <c r="BA4" s="38"/>
       <c r="BB4" s="38"/>
       <c r="BC4" s="38"/>
       <c r="BD4" s="38"/>
-      <c r="BE4" s="91"/>
-      <c r="BF4" s="92"/>
+      <c r="BE4" s="103"/>
+      <c r="BF4" s="104"/>
       <c r="BG4" s="38"/>
       <c r="BH4" s="38"/>
       <c r="BI4" s="38"/>
       <c r="BJ4" s="38"/>
       <c r="BK4" s="38"/>
-      <c r="BL4" s="92"/>
+      <c r="BL4" s="104"/>
       <c r="BM4" s="38"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5102,29 +5324,29 @@
       </c>
       <c r="C5" s="37"/>
       <c r="D5" s="37"/>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="56" t="n">
+      <c r="G5" s="98" t="n">
         <f aca="false">Netzplan!G5</f>
         <v>3</v>
       </c>
-      <c r="H5" s="57" t="n">
+      <c r="H5" s="99" t="n">
         <f aca="false">Netzplan!H5</f>
         <v>2</v>
       </c>
-      <c r="I5" s="58" t="n">
+      <c r="I5" s="100" t="n">
         <f aca="false">Netzplan!I5</f>
         <v>0.6</v>
       </c>
-      <c r="J5" s="89" t="n">
+      <c r="J5" s="101" t="n">
         <f aca="false">Netzplan!J5</f>
         <v>3</v>
       </c>
-      <c r="K5" s="90" t="n">
+      <c r="K5" s="102" t="n">
         <f aca="false">SUM(L5:BM5)</f>
         <v>3</v>
       </c>
@@ -5142,15 +5364,15 @@
       <c r="S5" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
+      <c r="T5" s="98"/>
+      <c r="U5" s="98"/>
+      <c r="V5" s="98"/>
       <c r="W5" s="38"/>
       <c r="X5" s="38"/>
       <c r="Y5" s="38"/>
       <c r="Z5" s="38"/>
       <c r="AA5" s="38"/>
-      <c r="AB5" s="91"/>
+      <c r="AB5" s="103"/>
       <c r="AC5" s="38"/>
       <c r="AD5" s="38"/>
       <c r="AE5" s="38"/>
@@ -5158,7 +5380,7 @@
       <c r="AG5" s="38"/>
       <c r="AH5" s="38"/>
       <c r="AI5" s="38"/>
-      <c r="AJ5" s="91"/>
+      <c r="AJ5" s="103"/>
       <c r="AK5" s="38"/>
       <c r="AL5" s="38"/>
       <c r="AM5" s="38"/>
@@ -5173,20 +5395,20 @@
       <c r="AV5" s="38"/>
       <c r="AW5" s="38"/>
       <c r="AX5" s="38"/>
-      <c r="AY5" s="92"/>
+      <c r="AY5" s="104"/>
       <c r="AZ5" s="38"/>
       <c r="BA5" s="38"/>
       <c r="BB5" s="38"/>
       <c r="BC5" s="38"/>
       <c r="BD5" s="38"/>
-      <c r="BE5" s="91"/>
-      <c r="BF5" s="92"/>
+      <c r="BE5" s="103"/>
+      <c r="BF5" s="104"/>
       <c r="BG5" s="38"/>
       <c r="BH5" s="38"/>
       <c r="BI5" s="38"/>
       <c r="BJ5" s="38"/>
       <c r="BK5" s="38"/>
-      <c r="BL5" s="92"/>
+      <c r="BL5" s="104"/>
       <c r="BM5" s="38"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5198,29 +5420,29 @@
       </c>
       <c r="C6" s="37"/>
       <c r="D6" s="37"/>
-      <c r="E6" s="71" t="s">
+      <c r="E6" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="56" t="n">
+      <c r="G6" s="98" t="n">
         <f aca="false">Netzplan!G6</f>
         <v>7</v>
       </c>
-      <c r="H6" s="57" t="n">
+      <c r="H6" s="99" t="n">
         <f aca="false">Netzplan!H6</f>
         <v>1</v>
       </c>
-      <c r="I6" s="58" t="n">
+      <c r="I6" s="100" t="n">
         <f aca="false">Netzplan!I6</f>
         <v>1.5</v>
       </c>
-      <c r="J6" s="89" t="n">
+      <c r="J6" s="101" t="n">
         <f aca="false">Netzplan!J6</f>
         <v>5</v>
       </c>
-      <c r="K6" s="90" t="n">
+      <c r="K6" s="102" t="n">
         <f aca="false">SUM(L6:BM6)</f>
         <v>5</v>
       </c>
@@ -5241,24 +5463,24 @@
       <c r="V6" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="W6" s="56" t="n">
+      <c r="W6" s="98" t="n">
         <v>1</v>
       </c>
       <c r="X6" s="38"/>
       <c r="Y6" s="38"/>
-      <c r="Z6" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="93"/>
-      <c r="AC6" s="56"/>
+      <c r="Z6" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="98"/>
+      <c r="AB6" s="107"/>
+      <c r="AC6" s="98"/>
       <c r="AD6" s="38"/>
       <c r="AE6" s="38"/>
       <c r="AF6" s="38"/>
       <c r="AG6" s="38"/>
       <c r="AH6" s="38"/>
       <c r="AI6" s="38"/>
-      <c r="AJ6" s="91"/>
+      <c r="AJ6" s="103"/>
       <c r="AK6" s="38"/>
       <c r="AL6" s="38"/>
       <c r="AM6" s="38"/>
@@ -5273,20 +5495,20 @@
       <c r="AV6" s="38"/>
       <c r="AW6" s="38"/>
       <c r="AX6" s="38"/>
-      <c r="AY6" s="92"/>
+      <c r="AY6" s="104"/>
       <c r="AZ6" s="38"/>
       <c r="BA6" s="38"/>
       <c r="BB6" s="38"/>
       <c r="BC6" s="38"/>
       <c r="BD6" s="38"/>
-      <c r="BE6" s="91"/>
-      <c r="BF6" s="92"/>
+      <c r="BE6" s="103"/>
+      <c r="BF6" s="104"/>
       <c r="BG6" s="38"/>
       <c r="BH6" s="38"/>
       <c r="BI6" s="38"/>
       <c r="BJ6" s="38"/>
       <c r="BK6" s="38"/>
-      <c r="BL6" s="92"/>
+      <c r="BL6" s="104"/>
       <c r="BM6" s="38"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5298,29 +5520,29 @@
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="37"/>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="56" t="n">
+      <c r="G7" s="98" t="n">
         <f aca="false">Netzplan!G7</f>
         <v>1</v>
       </c>
-      <c r="H7" s="56" t="str">
+      <c r="H7" s="98" t="str">
         <f aca="false">Netzplan!H7</f>
         <v>1</v>
       </c>
-      <c r="I7" s="58" t="n">
+      <c r="I7" s="100" t="n">
         <f aca="false">Netzplan!I7</f>
         <v>1</v>
       </c>
-      <c r="J7" s="89" t="n">
+      <c r="J7" s="101" t="n">
         <f aca="false">Netzplan!J7</f>
         <v>1</v>
       </c>
-      <c r="K7" s="90" t="n">
+      <c r="K7" s="102" t="n">
         <f aca="false">SUM(L7:BM7)</f>
         <v>1</v>
       </c>
@@ -5333,7 +5555,7 @@
       <c r="P7" s="38"/>
       <c r="Q7" s="38"/>
       <c r="R7" s="38"/>
-      <c r="S7" s="56"/>
+      <c r="S7" s="98"/>
       <c r="T7" s="38"/>
       <c r="U7" s="38"/>
       <c r="V7" s="38"/>
@@ -5342,7 +5564,7 @@
       <c r="Y7" s="38"/>
       <c r="Z7" s="38"/>
       <c r="AA7" s="38"/>
-      <c r="AB7" s="91"/>
+      <c r="AB7" s="103"/>
       <c r="AC7" s="38"/>
       <c r="AD7" s="38"/>
       <c r="AE7" s="38"/>
@@ -5350,7 +5572,7 @@
       <c r="AG7" s="38"/>
       <c r="AH7" s="38"/>
       <c r="AI7" s="38"/>
-      <c r="AJ7" s="91"/>
+      <c r="AJ7" s="103"/>
       <c r="AK7" s="38"/>
       <c r="AL7" s="38"/>
       <c r="AM7" s="38"/>
@@ -5365,20 +5587,20 @@
       <c r="AV7" s="38"/>
       <c r="AW7" s="38"/>
       <c r="AX7" s="38"/>
-      <c r="AY7" s="92"/>
+      <c r="AY7" s="104"/>
       <c r="AZ7" s="38"/>
       <c r="BA7" s="38"/>
       <c r="BB7" s="38"/>
       <c r="BC7" s="38"/>
       <c r="BD7" s="38"/>
-      <c r="BE7" s="91"/>
-      <c r="BF7" s="92"/>
+      <c r="BE7" s="103"/>
+      <c r="BF7" s="104"/>
       <c r="BG7" s="38"/>
       <c r="BH7" s="38"/>
       <c r="BI7" s="38"/>
       <c r="BJ7" s="38"/>
       <c r="BK7" s="38"/>
-      <c r="BL7" s="92"/>
+      <c r="BL7" s="104"/>
       <c r="BM7" s="38"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5390,29 +5612,29 @@
       </c>
       <c r="C8" s="37"/>
       <c r="D8" s="37"/>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="56" t="n">
+      <c r="G8" s="98" t="n">
         <f aca="false">Netzplan!G8</f>
         <v>3</v>
       </c>
-      <c r="H8" s="56" t="str">
+      <c r="H8" s="98" t="str">
         <f aca="false">Netzplan!H8</f>
         <v>1</v>
       </c>
-      <c r="I8" s="58" t="n">
+      <c r="I8" s="100" t="n">
         <f aca="false">Netzplan!I8</f>
         <v>0.8</v>
       </c>
-      <c r="J8" s="89" t="n">
+      <c r="J8" s="101" t="n">
         <f aca="false">Netzplan!J8</f>
         <v>4</v>
       </c>
-      <c r="K8" s="90" t="n">
+      <c r="K8" s="102" t="n">
         <f aca="false">SUM(L8:BM8)</f>
         <v>4</v>
       </c>
@@ -5430,17 +5652,17 @@
       <c r="S8" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="T8" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
+      <c r="T8" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
       <c r="W8" s="38"/>
       <c r="X8" s="38"/>
       <c r="Y8" s="38"/>
       <c r="Z8" s="38"/>
       <c r="AA8" s="38"/>
-      <c r="AB8" s="91"/>
+      <c r="AB8" s="103"/>
       <c r="AC8" s="38"/>
       <c r="AD8" s="38"/>
       <c r="AE8" s="38"/>
@@ -5448,7 +5670,7 @@
       <c r="AG8" s="38"/>
       <c r="AH8" s="38"/>
       <c r="AI8" s="38"/>
-      <c r="AJ8" s="91"/>
+      <c r="AJ8" s="103"/>
       <c r="AK8" s="38"/>
       <c r="AL8" s="38"/>
       <c r="AM8" s="38"/>
@@ -5463,36 +5685,36 @@
       <c r="AV8" s="38"/>
       <c r="AW8" s="38"/>
       <c r="AX8" s="38"/>
-      <c r="AY8" s="92"/>
+      <c r="AY8" s="104"/>
       <c r="AZ8" s="38"/>
       <c r="BA8" s="38"/>
       <c r="BB8" s="38"/>
       <c r="BC8" s="38"/>
       <c r="BD8" s="38"/>
-      <c r="BE8" s="91"/>
-      <c r="BF8" s="92"/>
+      <c r="BE8" s="103"/>
+      <c r="BF8" s="104"/>
       <c r="BG8" s="38"/>
       <c r="BH8" s="38"/>
       <c r="BI8" s="38"/>
       <c r="BJ8" s="38"/>
       <c r="BK8" s="38"/>
-      <c r="BL8" s="92"/>
+      <c r="BL8" s="104"/>
       <c r="BM8" s="38"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36"/>
-      <c r="B9" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="89"/>
-      <c r="K9" s="90"/>
+      <c r="B9" s="108" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="102"/>
       <c r="L9" s="38"/>
       <c r="M9" s="38"/>
       <c r="N9" s="38"/>
@@ -5501,15 +5723,15 @@
       <c r="Q9" s="38"/>
       <c r="R9" s="38"/>
       <c r="S9" s="38"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="56"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="98"/>
       <c r="W9" s="38"/>
       <c r="X9" s="38"/>
       <c r="Y9" s="38"/>
       <c r="Z9" s="38"/>
       <c r="AA9" s="38"/>
-      <c r="AB9" s="91"/>
+      <c r="AB9" s="103"/>
       <c r="AC9" s="38"/>
       <c r="AD9" s="38"/>
       <c r="AE9" s="38"/>
@@ -5517,7 +5739,7 @@
       <c r="AG9" s="38"/>
       <c r="AH9" s="38"/>
       <c r="AI9" s="38"/>
-      <c r="AJ9" s="91"/>
+      <c r="AJ9" s="103"/>
       <c r="AK9" s="38"/>
       <c r="AL9" s="38"/>
       <c r="AM9" s="38"/>
@@ -5532,20 +5754,20 @@
       <c r="AV9" s="38"/>
       <c r="AW9" s="38"/>
       <c r="AX9" s="38"/>
-      <c r="AY9" s="92"/>
+      <c r="AY9" s="104"/>
       <c r="AZ9" s="38"/>
       <c r="BA9" s="38"/>
       <c r="BB9" s="38"/>
       <c r="BC9" s="38"/>
       <c r="BD9" s="38"/>
-      <c r="BE9" s="91"/>
-      <c r="BF9" s="92"/>
+      <c r="BE9" s="103"/>
+      <c r="BF9" s="104"/>
       <c r="BG9" s="38"/>
       <c r="BH9" s="38"/>
       <c r="BI9" s="38"/>
       <c r="BJ9" s="38"/>
       <c r="BK9" s="38"/>
-      <c r="BL9" s="92"/>
+      <c r="BL9" s="104"/>
       <c r="BM9" s="38"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5557,29 +5779,29 @@
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="37"/>
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="106" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="71" t="s">
+      <c r="F10" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="56" t="n">
+      <c r="G10" s="98" t="n">
         <f aca="false">Netzplan!G9</f>
         <v>2</v>
       </c>
-      <c r="H10" s="56" t="str">
+      <c r="H10" s="98" t="str">
         <f aca="false">Netzplan!H9</f>
         <v>1</v>
       </c>
-      <c r="I10" s="58" t="n">
+      <c r="I10" s="100" t="n">
         <f aca="false">Netzplan!I9</f>
         <v>1.5</v>
       </c>
-      <c r="J10" s="89" t="n">
+      <c r="J10" s="101" t="n">
         <f aca="false">Netzplan!J9</f>
         <v>1</v>
       </c>
-      <c r="K10" s="90" t="n">
+      <c r="K10" s="102" t="n">
         <f aca="false">SUM(L10:BM10)</f>
         <v>1</v>
       </c>
@@ -5601,15 +5823,15 @@
       <c r="AA10" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="AB10" s="91"/>
+      <c r="AB10" s="103"/>
       <c r="AC10" s="38"/>
-      <c r="AD10" s="56"/>
+      <c r="AD10" s="98"/>
       <c r="AE10" s="38"/>
       <c r="AF10" s="38"/>
-      <c r="AG10" s="56"/>
+      <c r="AG10" s="98"/>
       <c r="AH10" s="38"/>
       <c r="AI10" s="38"/>
-      <c r="AJ10" s="91"/>
+      <c r="AJ10" s="103"/>
       <c r="AK10" s="38"/>
       <c r="AL10" s="38"/>
       <c r="AM10" s="38"/>
@@ -5624,20 +5846,20 @@
       <c r="AV10" s="38"/>
       <c r="AW10" s="38"/>
       <c r="AX10" s="38"/>
-      <c r="AY10" s="92"/>
+      <c r="AY10" s="104"/>
       <c r="AZ10" s="38"/>
       <c r="BA10" s="38"/>
       <c r="BB10" s="38"/>
       <c r="BC10" s="38"/>
       <c r="BD10" s="38"/>
-      <c r="BE10" s="91"/>
-      <c r="BF10" s="92"/>
+      <c r="BE10" s="103"/>
+      <c r="BF10" s="104"/>
       <c r="BG10" s="38"/>
       <c r="BH10" s="38"/>
       <c r="BI10" s="38"/>
       <c r="BJ10" s="38"/>
       <c r="BK10" s="38"/>
-      <c r="BL10" s="92"/>
+      <c r="BL10" s="104"/>
       <c r="BM10" s="38"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5649,29 +5871,29 @@
       </c>
       <c r="C11" s="37"/>
       <c r="D11" s="37"/>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="56" t="n">
+      <c r="G11" s="98" t="n">
         <f aca="false">Netzplan!G10</f>
         <v>2</v>
       </c>
-      <c r="H11" s="56" t="str">
+      <c r="H11" s="98" t="str">
         <f aca="false">Netzplan!H10</f>
         <v>1</v>
       </c>
-      <c r="I11" s="58" t="n">
+      <c r="I11" s="100" t="n">
         <f aca="false">Netzplan!I10</f>
         <v>1.5</v>
       </c>
-      <c r="J11" s="89" t="n">
+      <c r="J11" s="101" t="n">
         <f aca="false">Netzplan!J10</f>
         <v>1</v>
       </c>
-      <c r="K11" s="90" t="n">
+      <c r="K11" s="102" t="n">
         <f aca="false">SUM(L11:BM11)</f>
         <v>1</v>
       </c>
@@ -5691,7 +5913,7 @@
       <c r="Y11" s="38"/>
       <c r="Z11" s="38"/>
       <c r="AA11" s="38"/>
-      <c r="AB11" s="91"/>
+      <c r="AB11" s="103"/>
       <c r="AC11" s="38" t="n">
         <v>1</v>
       </c>
@@ -5699,9 +5921,9 @@
       <c r="AE11" s="38"/>
       <c r="AF11" s="38"/>
       <c r="AG11" s="38"/>
-      <c r="AH11" s="56"/>
-      <c r="AI11" s="56"/>
-      <c r="AJ11" s="91"/>
+      <c r="AH11" s="98"/>
+      <c r="AI11" s="98"/>
+      <c r="AJ11" s="103"/>
       <c r="AK11" s="38"/>
       <c r="AL11" s="38"/>
       <c r="AM11" s="38"/>
@@ -5716,20 +5938,20 @@
       <c r="AV11" s="38"/>
       <c r="AW11" s="38"/>
       <c r="AX11" s="38"/>
-      <c r="AY11" s="92"/>
+      <c r="AY11" s="104"/>
       <c r="AZ11" s="38"/>
       <c r="BA11" s="38"/>
       <c r="BB11" s="38"/>
       <c r="BC11" s="38"/>
       <c r="BD11" s="38"/>
-      <c r="BE11" s="91"/>
-      <c r="BF11" s="92"/>
+      <c r="BE11" s="103"/>
+      <c r="BF11" s="104"/>
       <c r="BG11" s="38"/>
       <c r="BH11" s="38"/>
       <c r="BI11" s="38"/>
       <c r="BJ11" s="38"/>
       <c r="BK11" s="38"/>
-      <c r="BL11" s="92"/>
+      <c r="BL11" s="104"/>
       <c r="BM11" s="38"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5741,29 +5963,29 @@
       </c>
       <c r="C12" s="37"/>
       <c r="D12" s="37"/>
-      <c r="E12" s="71" t="s">
+      <c r="E12" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="56" t="n">
+      <c r="G12" s="98" t="n">
         <f aca="false">Netzplan!G11</f>
         <v>2</v>
       </c>
-      <c r="H12" s="56" t="str">
+      <c r="H12" s="98" t="str">
         <f aca="false">Netzplan!H11</f>
         <v>1</v>
       </c>
-      <c r="I12" s="58" t="n">
+      <c r="I12" s="100" t="n">
         <f aca="false">Netzplan!I11</f>
         <v>1.5</v>
       </c>
-      <c r="J12" s="89" t="n">
+      <c r="J12" s="101" t="n">
         <f aca="false">Netzplan!J11</f>
         <v>1</v>
       </c>
-      <c r="K12" s="90" t="n">
+      <c r="K12" s="102" t="n">
         <f aca="false">SUM(L12:BM12)</f>
         <v>1</v>
       </c>
@@ -5783,7 +6005,7 @@
       <c r="Y12" s="38"/>
       <c r="Z12" s="38"/>
       <c r="AA12" s="38"/>
-      <c r="AB12" s="91"/>
+      <c r="AB12" s="103"/>
       <c r="AC12" s="38"/>
       <c r="AD12" s="38" t="n">
         <v>1</v>
@@ -5792,8 +6014,8 @@
       <c r="AF12" s="38"/>
       <c r="AG12" s="38"/>
       <c r="AH12" s="38"/>
-      <c r="AJ12" s="93"/>
-      <c r="AK12" s="56"/>
+      <c r="AJ12" s="107"/>
+      <c r="AK12" s="98"/>
       <c r="AL12" s="38"/>
       <c r="AM12" s="38"/>
       <c r="AN12" s="38"/>
@@ -5807,20 +6029,20 @@
       <c r="AV12" s="38"/>
       <c r="AW12" s="38"/>
       <c r="AX12" s="38"/>
-      <c r="AY12" s="92"/>
+      <c r="AY12" s="104"/>
       <c r="AZ12" s="38"/>
       <c r="BA12" s="38"/>
       <c r="BB12" s="38"/>
       <c r="BC12" s="38"/>
       <c r="BD12" s="38"/>
-      <c r="BE12" s="91"/>
-      <c r="BF12" s="92"/>
+      <c r="BE12" s="103"/>
+      <c r="BF12" s="104"/>
       <c r="BG12" s="38"/>
       <c r="BH12" s="38"/>
       <c r="BI12" s="38"/>
       <c r="BJ12" s="38"/>
       <c r="BK12" s="38"/>
-      <c r="BL12" s="92"/>
+      <c r="BL12" s="104"/>
       <c r="BM12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5832,29 +6054,29 @@
       </c>
       <c r="C13" s="37"/>
       <c r="D13" s="37"/>
-      <c r="E13" s="71" t="s">
+      <c r="E13" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="71" t="s">
+      <c r="F13" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="56" t="n">
+      <c r="G13" s="98" t="n">
         <f aca="false">Netzplan!G12</f>
         <v>10</v>
       </c>
-      <c r="H13" s="57" t="n">
+      <c r="H13" s="99" t="n">
         <f aca="false">Netzplan!H12</f>
         <v>1</v>
       </c>
-      <c r="I13" s="58" t="n">
+      <c r="I13" s="100" t="n">
         <f aca="false">Netzplan!I12</f>
         <v>0.5</v>
       </c>
-      <c r="J13" s="89" t="n">
+      <c r="J13" s="101" t="n">
         <f aca="false">Netzplan!J12</f>
         <v>20</v>
       </c>
-      <c r="K13" s="90" t="n">
+      <c r="K13" s="102" t="n">
         <f aca="false">SUM(L13:BM13)</f>
         <v>20</v>
       </c>
@@ -5873,7 +6095,7 @@
       <c r="V13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="W13" s="56" t="n">
+      <c r="W13" s="98" t="n">
         <v>1</v>
       </c>
       <c r="X13" s="38"/>
@@ -5884,26 +6106,26 @@
       <c r="AA13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="AB13" s="91"/>
+      <c r="AB13" s="103"/>
       <c r="AC13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="AD13" s="56" t="n">
+      <c r="AD13" s="98" t="n">
         <v>1</v>
       </c>
       <c r="AE13" s="38"/>
       <c r="AF13" s="38"/>
-      <c r="AG13" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" s="56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" s="93"/>
-      <c r="AK13" s="56" t="n">
+      <c r="AG13" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="107"/>
+      <c r="AK13" s="98" t="n">
         <v>1</v>
       </c>
       <c r="AL13" s="38"/>
@@ -5920,7 +6142,7 @@
       <c r="AQ13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="AR13" s="56" t="n">
+      <c r="AR13" s="98" t="n">
         <v>1</v>
       </c>
       <c r="AS13" s="38"/>
@@ -5937,19 +6159,19 @@
       <c r="AX13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="AY13" s="92"/>
+      <c r="AY13" s="104"/>
       <c r="AZ13" s="38"/>
       <c r="BA13" s="38"/>
       <c r="BB13" s="38"/>
       <c r="BC13" s="38"/>
       <c r="BD13" s="38"/>
-      <c r="BE13" s="91"/>
-      <c r="BF13" s="92"/>
+      <c r="BE13" s="103"/>
+      <c r="BF13" s="104"/>
       <c r="BG13" s="38"/>
       <c r="BH13" s="38"/>
       <c r="BJ13" s="38"/>
       <c r="BK13" s="38"/>
-      <c r="BL13" s="92"/>
+      <c r="BL13" s="104"/>
       <c r="BM13" s="38"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5961,29 +6183,29 @@
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
-      <c r="E14" s="71" t="s">
+      <c r="E14" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="71" t="s">
+      <c r="F14" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="56" t="n">
+      <c r="G14" s="98" t="n">
         <f aca="false">Netzplan!G13</f>
         <v>3</v>
       </c>
-      <c r="H14" s="56" t="str">
+      <c r="H14" s="98" t="str">
         <f aca="false">Netzplan!H13</f>
         <v>1</v>
       </c>
-      <c r="I14" s="58" t="n">
+      <c r="I14" s="100" t="n">
         <f aca="false">Netzplan!I13</f>
         <v>1.5</v>
       </c>
-      <c r="J14" s="89" t="n">
+      <c r="J14" s="101" t="n">
         <f aca="false">Netzplan!J13</f>
         <v>2</v>
       </c>
-      <c r="K14" s="90" t="n">
+      <c r="K14" s="102" t="n">
         <f aca="false">SUM(L14:BM14)</f>
         <v>2</v>
       </c>
@@ -6003,7 +6225,7 @@
       <c r="Y14" s="38"/>
       <c r="Z14" s="38"/>
       <c r="AA14" s="38"/>
-      <c r="AB14" s="91"/>
+      <c r="AB14" s="103"/>
       <c r="AC14" s="38"/>
       <c r="AD14" s="38"/>
       <c r="AE14" s="38"/>
@@ -6015,12 +6237,12 @@
         <v>1</v>
       </c>
       <c r="AI14" s="38"/>
-      <c r="AJ14" s="91"/>
+      <c r="AJ14" s="103"/>
       <c r="AL14" s="38"/>
       <c r="AM14" s="38"/>
-      <c r="AN14" s="56"/>
-      <c r="AO14" s="56"/>
-      <c r="AP14" s="56"/>
+      <c r="AN14" s="98"/>
+      <c r="AO14" s="98"/>
+      <c r="AP14" s="98"/>
       <c r="AQ14" s="38"/>
       <c r="AR14" s="38"/>
       <c r="AS14" s="38"/>
@@ -6029,20 +6251,20 @@
       <c r="AV14" s="38"/>
       <c r="AW14" s="38"/>
       <c r="AX14" s="38"/>
-      <c r="AY14" s="92"/>
+      <c r="AY14" s="104"/>
       <c r="AZ14" s="38"/>
       <c r="BA14" s="38"/>
       <c r="BB14" s="38"/>
       <c r="BC14" s="38"/>
       <c r="BD14" s="38"/>
-      <c r="BE14" s="91"/>
-      <c r="BF14" s="92"/>
+      <c r="BE14" s="103"/>
+      <c r="BF14" s="104"/>
       <c r="BG14" s="38"/>
       <c r="BH14" s="38"/>
       <c r="BI14" s="38"/>
       <c r="BJ14" s="38"/>
       <c r="BK14" s="38"/>
-      <c r="BL14" s="92"/>
+      <c r="BL14" s="104"/>
       <c r="BM14" s="38"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6054,29 +6276,29 @@
       </c>
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
-      <c r="E15" s="71" t="s">
+      <c r="E15" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="56" t="n">
+      <c r="G15" s="98" t="n">
         <f aca="false">Netzplan!G14</f>
         <v>3</v>
       </c>
-      <c r="H15" s="56" t="str">
+      <c r="H15" s="98" t="str">
         <f aca="false">Netzplan!H14</f>
         <v>1</v>
       </c>
-      <c r="I15" s="58" t="n">
+      <c r="I15" s="100" t="n">
         <f aca="false">Netzplan!I14</f>
         <v>1.5</v>
       </c>
-      <c r="J15" s="89" t="n">
+      <c r="J15" s="101" t="n">
         <f aca="false">Netzplan!J14</f>
         <v>2</v>
       </c>
-      <c r="K15" s="90" t="n">
+      <c r="K15" s="102" t="n">
         <f aca="false">SUM(L15:BM15)</f>
         <v>2</v>
       </c>
@@ -6096,7 +6318,7 @@
       <c r="Y15" s="38"/>
       <c r="Z15" s="38"/>
       <c r="AA15" s="38"/>
-      <c r="AB15" s="91"/>
+      <c r="AB15" s="103"/>
       <c r="AC15" s="38"/>
       <c r="AD15" s="38"/>
       <c r="AE15" s="38"/>
@@ -6106,7 +6328,7 @@
       <c r="AI15" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="AJ15" s="91"/>
+      <c r="AJ15" s="103"/>
       <c r="AK15" s="38" t="n">
         <v>1</v>
       </c>
@@ -6114,44 +6336,44 @@
       <c r="AM15" s="38"/>
       <c r="AN15" s="38"/>
       <c r="AO15" s="38"/>
-      <c r="AQ15" s="56"/>
-      <c r="AR15" s="56"/>
+      <c r="AQ15" s="98"/>
+      <c r="AR15" s="98"/>
       <c r="AS15" s="38"/>
       <c r="AT15" s="38"/>
-      <c r="AU15" s="56"/>
+      <c r="AU15" s="98"/>
       <c r="AV15" s="38"/>
       <c r="AW15" s="38"/>
       <c r="AX15" s="38"/>
-      <c r="AY15" s="92"/>
+      <c r="AY15" s="104"/>
       <c r="AZ15" s="38"/>
       <c r="BA15" s="38"/>
       <c r="BB15" s="38"/>
       <c r="BC15" s="38"/>
       <c r="BD15" s="38"/>
-      <c r="BE15" s="91"/>
-      <c r="BF15" s="92"/>
+      <c r="BE15" s="103"/>
+      <c r="BF15" s="104"/>
       <c r="BG15" s="38"/>
       <c r="BH15" s="38"/>
       <c r="BI15" s="38"/>
       <c r="BJ15" s="38"/>
       <c r="BK15" s="38"/>
-      <c r="BL15" s="92"/>
+      <c r="BL15" s="104"/>
       <c r="BM15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36"/>
-      <c r="B16" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="89"/>
-      <c r="K16" s="90"/>
+      <c r="B16" s="108" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="101"/>
+      <c r="K16" s="102"/>
       <c r="L16" s="38"/>
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
@@ -6168,7 +6390,7 @@
       <c r="Y16" s="38"/>
       <c r="Z16" s="38"/>
       <c r="AA16" s="38"/>
-      <c r="AB16" s="91"/>
+      <c r="AB16" s="103"/>
       <c r="AC16" s="38"/>
       <c r="AD16" s="38"/>
       <c r="AE16" s="38"/>
@@ -6176,34 +6398,34 @@
       <c r="AG16" s="38"/>
       <c r="AH16" s="38"/>
       <c r="AI16" s="38"/>
-      <c r="AJ16" s="91"/>
+      <c r="AJ16" s="103"/>
       <c r="AK16" s="38"/>
       <c r="AL16" s="38"/>
       <c r="AM16" s="38"/>
       <c r="AN16" s="38"/>
       <c r="AO16" s="38"/>
-      <c r="AQ16" s="56"/>
-      <c r="AR16" s="56"/>
+      <c r="AQ16" s="98"/>
+      <c r="AR16" s="98"/>
       <c r="AS16" s="38"/>
       <c r="AT16" s="38"/>
-      <c r="AU16" s="56"/>
+      <c r="AU16" s="98"/>
       <c r="AV16" s="38"/>
       <c r="AW16" s="38"/>
       <c r="AX16" s="38"/>
-      <c r="AY16" s="92"/>
+      <c r="AY16" s="104"/>
       <c r="AZ16" s="38"/>
       <c r="BA16" s="38"/>
       <c r="BB16" s="38"/>
       <c r="BC16" s="38"/>
       <c r="BD16" s="38"/>
-      <c r="BE16" s="91"/>
-      <c r="BF16" s="92"/>
+      <c r="BE16" s="103"/>
+      <c r="BF16" s="104"/>
       <c r="BG16" s="38"/>
       <c r="BH16" s="38"/>
       <c r="BI16" s="38"/>
       <c r="BJ16" s="38"/>
       <c r="BK16" s="38"/>
-      <c r="BL16" s="92"/>
+      <c r="BL16" s="104"/>
       <c r="BM16" s="38"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6215,29 +6437,29 @@
       </c>
       <c r="C17" s="37"/>
       <c r="D17" s="37"/>
-      <c r="E17" s="71" t="s">
+      <c r="E17" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="71" t="s">
+      <c r="F17" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="56" t="n">
+      <c r="G17" s="98" t="n">
         <f aca="false">Netzplan!G15</f>
         <v>1</v>
       </c>
-      <c r="H17" s="56" t="str">
+      <c r="H17" s="98" t="str">
         <f aca="false">Netzplan!H15</f>
         <v>1</v>
       </c>
-      <c r="I17" s="58" t="n">
+      <c r="I17" s="100" t="n">
         <f aca="false">Netzplan!I15</f>
         <v>1.5</v>
       </c>
-      <c r="J17" s="89" t="n">
+      <c r="J17" s="101" t="n">
         <f aca="false">Netzplan!J15</f>
         <v>1</v>
       </c>
-      <c r="K17" s="90" t="n">
+      <c r="K17" s="102" t="n">
         <f aca="false">SUM(L17:BM17)</f>
         <v>1</v>
       </c>
@@ -6257,7 +6479,7 @@
       <c r="Y17" s="38"/>
       <c r="Z17" s="38"/>
       <c r="AA17" s="38"/>
-      <c r="AB17" s="91"/>
+      <c r="AB17" s="103"/>
       <c r="AC17" s="38"/>
       <c r="AD17" s="38"/>
       <c r="AE17" s="38"/>
@@ -6265,11 +6487,10 @@
       <c r="AG17" s="38"/>
       <c r="AH17" s="38"/>
       <c r="AI17" s="38"/>
-      <c r="AJ17" s="91"/>
+      <c r="AJ17" s="103"/>
       <c r="AK17" s="38"/>
       <c r="AL17" s="38"/>
       <c r="AM17" s="38"/>
-      <c r="AN17" s="0"/>
       <c r="AO17" s="38"/>
       <c r="AP17" s="38"/>
       <c r="AQ17" s="38"/>
@@ -6279,23 +6500,23 @@
       <c r="AS17" s="38"/>
       <c r="AT17" s="38"/>
       <c r="AU17" s="38"/>
-      <c r="AV17" s="56"/>
+      <c r="AV17" s="98"/>
       <c r="AW17" s="38"/>
       <c r="AX17" s="38"/>
-      <c r="AY17" s="92"/>
+      <c r="AY17" s="104"/>
       <c r="AZ17" s="38"/>
       <c r="BA17" s="38"/>
       <c r="BB17" s="38"/>
       <c r="BC17" s="38"/>
       <c r="BD17" s="38"/>
-      <c r="BE17" s="91"/>
-      <c r="BF17" s="92"/>
+      <c r="BE17" s="103"/>
+      <c r="BF17" s="104"/>
       <c r="BG17" s="38"/>
       <c r="BH17" s="38"/>
       <c r="BI17" s="38"/>
       <c r="BJ17" s="38"/>
       <c r="BK17" s="38"/>
-      <c r="BL17" s="92"/>
+      <c r="BL17" s="104"/>
       <c r="BM17" s="38"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6307,29 +6528,29 @@
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
-      <c r="E18" s="71" t="s">
+      <c r="E18" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="56" t="n">
+      <c r="G18" s="98" t="n">
         <f aca="false">Netzplan!G16</f>
         <v>5</v>
       </c>
-      <c r="H18" s="56" t="str">
+      <c r="H18" s="98" t="str">
         <f aca="false">Netzplan!H16</f>
         <v>1</v>
       </c>
-      <c r="I18" s="58" t="n">
+      <c r="I18" s="100" t="n">
         <f aca="false">Netzplan!I16</f>
         <v>1.5</v>
       </c>
-      <c r="J18" s="89" t="n">
+      <c r="J18" s="101" t="n">
         <f aca="false">Netzplan!J16</f>
         <v>3</v>
       </c>
-      <c r="K18" s="90" t="n">
+      <c r="K18" s="102" t="n">
         <f aca="false">SUM(L18:BM18)</f>
         <v>3</v>
       </c>
@@ -6349,7 +6570,7 @@
       <c r="Y18" s="38"/>
       <c r="Z18" s="38"/>
       <c r="AA18" s="38"/>
-      <c r="AB18" s="91"/>
+      <c r="AB18" s="103"/>
       <c r="AC18" s="38"/>
       <c r="AD18" s="38"/>
       <c r="AE18" s="38"/>
@@ -6357,7 +6578,7 @@
       <c r="AG18" s="38"/>
       <c r="AH18" s="38"/>
       <c r="AI18" s="38"/>
-      <c r="AJ18" s="91"/>
+      <c r="AJ18" s="103"/>
       <c r="AK18" s="38"/>
       <c r="AL18" s="38"/>
       <c r="AM18" s="38"/>
@@ -6365,7 +6586,7 @@
       <c r="AO18" s="38"/>
       <c r="AP18" s="38"/>
       <c r="AQ18" s="38"/>
-      <c r="AR18" s="56"/>
+      <c r="AR18" s="98"/>
       <c r="AS18" s="38"/>
       <c r="AT18" s="38"/>
       <c r="AU18" s="38" t="n">
@@ -6377,36 +6598,36 @@
       <c r="AW18" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="AX18" s="56"/>
-      <c r="AY18" s="92"/>
+      <c r="AX18" s="98"/>
+      <c r="AY18" s="104"/>
       <c r="AZ18" s="38"/>
       <c r="BA18" s="38"/>
-      <c r="BB18" s="56"/>
+      <c r="BB18" s="98"/>
       <c r="BC18" s="38"/>
       <c r="BD18" s="38"/>
-      <c r="BE18" s="91"/>
-      <c r="BF18" s="92"/>
+      <c r="BE18" s="103"/>
+      <c r="BF18" s="104"/>
       <c r="BG18" s="38"/>
       <c r="BH18" s="38"/>
       <c r="BI18" s="38"/>
       <c r="BK18" s="38"/>
-      <c r="BL18" s="92"/>
+      <c r="BL18" s="104"/>
       <c r="BM18" s="38"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36"/>
-      <c r="B19" s="94" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="90"/>
+      <c r="B19" s="108" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="102"/>
       <c r="L19" s="38"/>
       <c r="M19" s="38"/>
       <c r="N19" s="38"/>
@@ -6423,7 +6644,7 @@
       <c r="Y19" s="38"/>
       <c r="Z19" s="38"/>
       <c r="AA19" s="38"/>
-      <c r="AB19" s="91"/>
+      <c r="AB19" s="103"/>
       <c r="AC19" s="38"/>
       <c r="AD19" s="38"/>
       <c r="AE19" s="38"/>
@@ -6431,7 +6652,7 @@
       <c r="AG19" s="38"/>
       <c r="AH19" s="38"/>
       <c r="AI19" s="38"/>
-      <c r="AJ19" s="91"/>
+      <c r="AJ19" s="103"/>
       <c r="AK19" s="38"/>
       <c r="AL19" s="38"/>
       <c r="AM19" s="38"/>
@@ -6439,26 +6660,26 @@
       <c r="AO19" s="38"/>
       <c r="AP19" s="38"/>
       <c r="AQ19" s="38"/>
-      <c r="AR19" s="56"/>
+      <c r="AR19" s="98"/>
       <c r="AS19" s="38"/>
       <c r="AT19" s="38"/>
       <c r="AU19" s="38"/>
       <c r="AV19" s="38"/>
       <c r="AW19" s="38"/>
-      <c r="AX19" s="56"/>
-      <c r="AY19" s="92"/>
+      <c r="AX19" s="98"/>
+      <c r="AY19" s="104"/>
       <c r="AZ19" s="38"/>
       <c r="BA19" s="38"/>
-      <c r="BB19" s="56"/>
+      <c r="BB19" s="98"/>
       <c r="BC19" s="38"/>
       <c r="BD19" s="38"/>
-      <c r="BE19" s="91"/>
-      <c r="BF19" s="92"/>
+      <c r="BE19" s="103"/>
+      <c r="BF19" s="104"/>
       <c r="BG19" s="38"/>
       <c r="BH19" s="38"/>
       <c r="BI19" s="38"/>
       <c r="BK19" s="38"/>
-      <c r="BL19" s="92"/>
+      <c r="BL19" s="104"/>
       <c r="BM19" s="38"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6470,27 +6691,27 @@
       </c>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="78"/>
-      <c r="G20" s="79" t="n">
+      <c r="F20" s="110"/>
+      <c r="G20" s="111" t="n">
         <f aca="false">Netzplan!G17</f>
         <v>1</v>
       </c>
-      <c r="H20" s="79" t="str">
+      <c r="H20" s="111" t="str">
         <f aca="false">Netzplan!H17</f>
         <v>1</v>
       </c>
-      <c r="I20" s="95" t="n">
+      <c r="I20" s="112" t="n">
         <f aca="false">Netzplan!I17</f>
         <v>1</v>
       </c>
-      <c r="J20" s="96" t="n">
+      <c r="J20" s="113" t="n">
         <f aca="false">Netzplan!J17</f>
         <v>1</v>
       </c>
-      <c r="K20" s="90" t="n">
+      <c r="K20" s="102" t="n">
         <f aca="false">SUM(L20:BM20)</f>
         <v>1</v>
       </c>
@@ -6510,7 +6731,7 @@
       <c r="Y20" s="42"/>
       <c r="Z20" s="42"/>
       <c r="AA20" s="42"/>
-      <c r="AB20" s="97"/>
+      <c r="AB20" s="114"/>
       <c r="AC20" s="42"/>
       <c r="AD20" s="42"/>
       <c r="AE20" s="42"/>
@@ -6518,7 +6739,7 @@
       <c r="AG20" s="42"/>
       <c r="AH20" s="42"/>
       <c r="AI20" s="42"/>
-      <c r="AJ20" s="97"/>
+      <c r="AJ20" s="114"/>
       <c r="AK20" s="42"/>
       <c r="AL20" s="42"/>
       <c r="AM20" s="42"/>
@@ -6533,22 +6754,21 @@
       <c r="AV20" s="42"/>
       <c r="AW20" s="42"/>
       <c r="AX20" s="42"/>
-      <c r="AY20" s="0"/>
       <c r="AZ20" s="42"/>
       <c r="BA20" s="38"/>
-      <c r="BB20" s="98" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC20" s="56"/>
+      <c r="BB20" s="115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC20" s="98"/>
       <c r="BD20" s="42"/>
-      <c r="BE20" s="97"/>
-      <c r="BF20" s="98"/>
+      <c r="BE20" s="114"/>
+      <c r="BF20" s="115"/>
       <c r="BG20" s="42"/>
       <c r="BH20" s="42"/>
       <c r="BI20" s="42"/>
       <c r="BJ20" s="42"/>
       <c r="BK20" s="42"/>
-      <c r="BL20" s="98"/>
+      <c r="BL20" s="115"/>
       <c r="BM20" s="42"/>
     </row>
   </sheetData>
@@ -6606,9 +6826,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="99" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="116" width="8.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="44" width="23.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="44" width="23.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="44" width="11.53"/>
@@ -6616,280 +6836,280 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="99" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="83" t="s">
-        <v>105</v>
+      <c r="A1" s="116" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="90" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="100" t="n">
+      <c r="A2" s="117" t="n">
         <v>45297</v>
       </c>
-      <c r="B2" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="83" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="83" t="s">
+      <c r="B2" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="F2" s="101" t="n">
+      <c r="C2" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="90" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="118" t="n">
         <v>45413</v>
       </c>
-      <c r="G2" s="101" t="n">
+      <c r="G2" s="118" t="n">
         <v>45414</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="100" t="n">
+      <c r="A3" s="117" t="n">
         <v>45359</v>
       </c>
-      <c r="B3" s="99" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="83" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="83" t="s">
+      <c r="B3" s="116" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="83" t="s">
+      <c r="C3" s="90" t="s">
         <v>112</v>
       </c>
+      <c r="D3" s="90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="90" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="100" t="n">
+      <c r="A4" s="117" t="n">
         <v>45380</v>
       </c>
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="116" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="83" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="83" t="s">
-        <v>115</v>
+      <c r="E4" s="90" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="100" t="n">
+      <c r="A5" s="117" t="n">
         <v>45383</v>
       </c>
-      <c r="B5" s="99" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="83" t="s">
+      <c r="B5" s="116" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="90" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" s="83" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="100" t="n">
+      <c r="A6" s="117" t="n">
         <v>45413</v>
       </c>
-      <c r="B6" s="99" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>115</v>
+      <c r="B6" s="116" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="90" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="90" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="100" t="n">
+      <c r="A7" s="117" t="n">
         <v>45421</v>
       </c>
-      <c r="B7" s="99" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="83" t="s">
+      <c r="B7" s="116" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="83" t="s">
-        <v>115</v>
+      <c r="C7" s="90" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="90" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="90" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="100" t="n">
+      <c r="A8" s="117" t="n">
         <v>45432</v>
       </c>
-      <c r="B8" s="99" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="83" t="s">
+      <c r="B8" s="116" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="90" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="117" t="n">
+        <v>45442</v>
+      </c>
+      <c r="B9" s="116" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" s="83" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="100" t="n">
-        <v>45442</v>
-      </c>
-      <c r="B9" s="99" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="83" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="83" t="s">
-        <v>127</v>
+      <c r="E9" s="90" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="100" t="n">
+      <c r="A10" s="117" t="n">
         <v>45519</v>
       </c>
-      <c r="B10" s="99" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="83" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="83" t="s">
+      <c r="B10" s="116" t="s">
         <v>130</v>
       </c>
+      <c r="C10" s="90" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="90" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="100" t="n">
+      <c r="A11" s="117" t="n">
         <v>45555</v>
       </c>
-      <c r="B11" s="99" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" s="83" t="s">
+      <c r="B11" s="116" t="s">
         <v>133</v>
       </c>
+      <c r="C11" s="90" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="90" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="100" t="n">
+      <c r="A12" s="117" t="n">
         <v>45568</v>
       </c>
-      <c r="B12" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="83" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="83" t="s">
-        <v>115</v>
+      <c r="B12" s="116" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="90" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="90" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="100" t="n">
+      <c r="A13" s="117" t="n">
         <v>45596</v>
       </c>
-      <c r="B13" s="99" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="83" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" s="99" t="s">
+      <c r="B13" s="116" t="s">
         <v>138</v>
       </c>
+      <c r="C13" s="90" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="90" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="116" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="101" t="n">
+      <c r="A14" s="118" t="n">
         <v>45597</v>
       </c>
-      <c r="B14" s="99" t="s">
+      <c r="B14" s="116" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="83" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" s="83" t="s">
-        <v>140</v>
+      <c r="D14" s="90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="90" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="101" t="n">
+      <c r="A15" s="118" t="n">
         <v>45616</v>
       </c>
-      <c r="B15" s="99" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="83" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="83" t="s">
+      <c r="B15" s="116" t="s">
         <v>143</v>
       </c>
+      <c r="C15" s="90" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="90" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="101" t="n">
+      <c r="A16" s="118" t="n">
         <v>45651</v>
       </c>
-      <c r="B16" s="99" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="83" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="83" t="s">
-        <v>115</v>
+      <c r="B16" s="116" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="90" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="90" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="101" t="n">
+      <c r="A17" s="118" t="n">
         <v>45652</v>
       </c>
-      <c r="B17" s="99" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="83" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" s="83" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="83" t="s">
+      <c r="B17" s="116" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="90" t="s">
         <v>147</v>
+      </c>
+      <c r="D17" s="90" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="90" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="90" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
